--- a/ZonasEscolares/excels/LIMA-LIMA-SAN_MARTIN_DE_PORRES.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-SAN_MARTIN_DE_PORRES.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5344,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6592,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7008,7 +7008,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7528,7 +7528,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7580,7 +7580,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7632,7 +7632,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7944,7 +7944,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8464,7 +8464,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8620,7 +8620,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8984,7 +8984,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>SAN_MARTIN_DE_PORRES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-SAN_MARTIN_DE_PORRES.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-SAN_MARTIN_DE_PORRES.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>VANGUARD SCHOOLS</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.01391</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-77.08557999999999</v>
-      </c>
-      <c r="I2" t="n">
-        <v>403</v>
-      </c>
-      <c r="J2" t="n">
-        <v>23</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.01391</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-77.08558</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>CARDANO VIETE INGENIEROS</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-11.99788</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-77.08956000000001</v>
-      </c>
-      <c r="I3" t="n">
-        <v>545</v>
-      </c>
-      <c r="J3" t="n">
-        <v>11</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-11.99788</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-77.08956</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>ANA MARIA RIVIER</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-11.97685</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-77.08641</v>
-      </c>
-      <c r="I4" t="n">
-        <v>203</v>
-      </c>
-      <c r="J4" t="n">
-        <v>24</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-11.97685</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-77.08641</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>EL NAZARENO</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-11.9633</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-77.09220000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>703</v>
-      </c>
-      <c r="J5" t="n">
-        <v>30</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-11.9633</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-77.0922</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>0005</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-11.94575</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-77.08906</v>
-      </c>
-      <c r="I6" t="n">
-        <v>317</v>
-      </c>
-      <c r="J6" t="n">
-        <v>15</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-11.94575</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-77.08906</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>0011 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.02932</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-77.06947</v>
-      </c>
-      <c r="I7" t="n">
-        <v>247</v>
-      </c>
-      <c r="J7" t="n">
-        <v>11</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.02932</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-77.06947</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>0020</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-11.99628</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-77.09407</v>
-      </c>
-      <c r="I8" t="n">
-        <v>202</v>
-      </c>
-      <c r="J8" t="n">
-        <v>10</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-11.99628</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-77.09407</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>0057</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.03451</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-77.05562999999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>347</v>
-      </c>
-      <c r="J9" t="n">
-        <v>17</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.03451</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-77.05563</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>0065</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.02645</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-77.06532</v>
-      </c>
-      <c r="I10" t="n">
-        <v>345</v>
-      </c>
-      <c r="J10" t="n">
-        <v>16</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.02645</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-77.06532</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>0081 LA SONRISA DE DIOS</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-12.019886</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-77.086935</v>
-      </c>
-      <c r="I11" t="n">
-        <v>258</v>
-      </c>
-      <c r="J11" t="n">
-        <v>13</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.019886</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-77.086935</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>0313</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-12.0364</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-77.0878</v>
-      </c>
-      <c r="I12" t="n">
-        <v>243</v>
-      </c>
-      <c r="J12" t="n">
-        <v>11</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.0364</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-77.0878</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>338 MANITOS CREATIVAS</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.02541</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-77.08014</v>
-      </c>
-      <c r="I13" t="n">
-        <v>230</v>
-      </c>
-      <c r="J13" t="n">
-        <v>11</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.02541</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-77.08014</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>0347 LUIS ENRIQUE XII</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-11.97135</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-77.10592</v>
-      </c>
-      <c r="I14" t="n">
-        <v>656</v>
-      </c>
-      <c r="J14" t="n">
-        <v>35</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-11.97135</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-77.10592</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>0358 NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.00635</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-77.09065</v>
-      </c>
-      <c r="I15" t="n">
-        <v>454</v>
-      </c>
-      <c r="J15" t="n">
-        <v>24</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.00635</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-77.09065</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>0361</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.02818</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-77.09079</v>
-      </c>
-      <c r="I16" t="n">
-        <v>208</v>
-      </c>
-      <c r="J16" t="n">
-        <v>11</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.02818</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-77.09079</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>2088 REPUBLICA FEDERAL DE ALEMANIA</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-11.95678</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-77.10062000000001</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1178</v>
-      </c>
-      <c r="J17" t="n">
-        <v>69</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-11.95678</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-77.10062</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1178</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>0387 NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-12.0062</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-77.08523</v>
-      </c>
-      <c r="I18" t="n">
-        <v>392</v>
-      </c>
-      <c r="J18" t="n">
-        <v>18</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.0062</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-77.08523</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>CONDEVILLA SEÑOR I</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-12.0214</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-77.0814</v>
-      </c>
-      <c r="I19" t="n">
-        <v>308</v>
-      </c>
-      <c r="J19" t="n">
-        <v>16</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-12.0214</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-77.0814</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>CONDEVILLA SEÑOR II</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-12.0243</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-77.0735</v>
-      </c>
-      <c r="I20" t="n">
-        <v>317</v>
-      </c>
-      <c r="J20" t="n">
-        <v>24</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.0243</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-77.0735</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>LUIS ENRIQUE XIX</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-12.01774</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-77.07859000000001</v>
-      </c>
-      <c r="I21" t="n">
-        <v>227</v>
-      </c>
-      <c r="J21" t="n">
-        <v>11</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-12.01774</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-77.07859</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>2001 SANTA ROSA DE LIMA</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-11.94492</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-77.08871000000001</v>
-      </c>
-      <c r="I22" t="n">
-        <v>849</v>
-      </c>
-      <c r="J22" t="n">
-        <v>46</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-11.94492</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-77.08871</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>2002 VIRGEN MARIA DEL ROSARIO</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-11.966955</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-77.08768499999999</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1263</v>
-      </c>
-      <c r="J23" t="n">
-        <v>56</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-11.966955</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-77.087685</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1263</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>2003 LIBERTADOR JOSE DE SAN MARTIN</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-12.0063</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-77.09099999999999</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1044</v>
-      </c>
-      <c r="J24" t="n">
-        <v>53</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-12.0063</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-77.091</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1044</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>2008 EL ROSARIO</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-12.02069</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-77.07389000000001</v>
-      </c>
-      <c r="I25" t="n">
-        <v>484</v>
-      </c>
-      <c r="J25" t="n">
-        <v>22</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-12.02069</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-77.07389</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>2074 VIRGEN PEREGRINA DEL ROSARIO</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-11.97756</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-77.08883</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1337</v>
-      </c>
-      <c r="J26" t="n">
-        <v>59</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-11.97756</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-77.08883</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1337</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>2010 ALBERT EINSTEIN</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-12.017275</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-77.08737499999999</v>
-      </c>
-      <c r="I27" t="n">
-        <v>455</v>
-      </c>
-      <c r="J27" t="n">
-        <v>12</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-12.017275</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-77.087375</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-12.0177</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-77.062</v>
-      </c>
-      <c r="I28" t="n">
-        <v>490</v>
-      </c>
-      <c r="J28" t="n">
-        <v>25</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-12.0177</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-77.062</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-12.03451</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-77.05606</v>
-      </c>
-      <c r="I29" t="n">
-        <v>327</v>
-      </c>
-      <c r="J29" t="n">
-        <v>14</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-12.03451</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-77.05606</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>2014 LOS CHASQUIS</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-11.993831</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-77.097146</v>
-      </c>
-      <c r="I30" t="n">
-        <v>346</v>
-      </c>
-      <c r="J30" t="n">
-        <v>14</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-11.993831</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-77.097146</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>2026 SAN DIEGO</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-11.94765</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-77.093</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1112</v>
-      </c>
-      <c r="J31" t="n">
-        <v>50</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-11.94765</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-77.093</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1112</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>2027 JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-12.0158</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-77.05705</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1253</v>
-      </c>
-      <c r="J32" t="n">
-        <v>65</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-12.0158</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-77.05705</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1253</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>2029 SIMON BOLIVAR</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-12.027</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-77.0667</v>
-      </c>
-      <c r="I33" t="n">
-        <v>799</v>
-      </c>
-      <c r="J33" t="n">
-        <v>52</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-12.027</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-77.0667</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>2030 VIRGEN DEL CARMEN</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-12.00012</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-77.08946</v>
-      </c>
-      <c r="I34" t="n">
-        <v>455</v>
-      </c>
-      <c r="J34" t="n">
-        <v>20</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-12.00012</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-77.08946</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>2031 VIRGEN DE FATIMA</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-11.98794</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-77.09218</v>
-      </c>
-      <c r="I35" t="n">
-        <v>900</v>
-      </c>
-      <c r="J35" t="n">
-        <v>41</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-11.98794</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-77.09218</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>2033 CARLOS HIRAOKA TORRES</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-11.98562</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-77.09974</v>
-      </c>
-      <c r="I36" t="n">
-        <v>542</v>
-      </c>
-      <c r="J36" t="n">
-        <v>25</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-11.98562</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-77.09974</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>2034 VIRGEN DE FATIMA</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-12.0115</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-77.05794</v>
-      </c>
-      <c r="I37" t="n">
-        <v>465</v>
-      </c>
-      <c r="J37" t="n">
-        <v>22</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-12.0115</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-77.05794</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>2072 MARIO VARGAS LLOSA</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-11.9982</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-77.0954</v>
-      </c>
-      <c r="I38" t="n">
-        <v>595</v>
-      </c>
-      <c r="J38" t="n">
-        <v>23</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-11.9982</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-77.0954</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>2082 HEROES DEL PACIFICO</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-12.00299</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-77.08484</v>
-      </c>
-      <c r="I39" t="n">
-        <v>570</v>
-      </c>
-      <c r="J39" t="n">
-        <v>29</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-12.00299</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-77.08484</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>LOS ALISOS</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-11.9848</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-77.087875</v>
-      </c>
-      <c r="I40" t="n">
-        <v>492</v>
-      </c>
-      <c r="J40" t="n">
-        <v>21</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-11.9848</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-77.087875</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>2094 INCA PACHACUTEC</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-12.02112</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-77.0788</v>
-      </c>
-      <c r="I41" t="n">
-        <v>629</v>
-      </c>
-      <c r="J41" t="n">
-        <v>37</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-12.02112</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-77.0788</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>2098 CABO JESUS VERA FERNANDEZ</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-12.01285</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-77.06807999999999</v>
-      </c>
-      <c r="I42" t="n">
-        <v>282</v>
-      </c>
-      <c r="J42" t="n">
-        <v>17</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-12.01285</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-77.06808</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>2101 MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-12.0158</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-77.07769999999999</v>
-      </c>
-      <c r="I43" t="n">
-        <v>517</v>
-      </c>
-      <c r="J43" t="n">
-        <v>24</v>
-      </c>
-      <c r="K43" t="n">
-        <v>1</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-12.0158</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-77.0777</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>3022 JOSE SABOGAL</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-12.03185</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-77.04595999999999</v>
-      </c>
-      <c r="I44" t="n">
-        <v>1155</v>
-      </c>
-      <c r="J44" t="n">
-        <v>60</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-12.03185</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-77.04596</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>3023 PEDRO E. PAULET MOSTAJO</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-12.0277</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-77.05759999999999</v>
-      </c>
-      <c r="I45" t="n">
-        <v>826</v>
-      </c>
-      <c r="J45" t="n">
-        <v>37</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-12.0277</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-77.0576</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>3027 CORONEL JOSE BALTA</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-12.03106</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-77.05296</v>
-      </c>
-      <c r="I46" t="n">
-        <v>403</v>
-      </c>
-      <c r="J46" t="n">
-        <v>33</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-12.03106</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-77.05296</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>3028 YACHAYHUASI</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-11.99239</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-77.08454999999999</v>
-      </c>
-      <c r="I47" t="n">
-        <v>387</v>
-      </c>
-      <c r="J47" t="n">
-        <v>16</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-11.99239</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-77.08455</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>3031 GRANDES TALENTOS</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-12.03674</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-77.04585</v>
-      </c>
-      <c r="I48" t="n">
-        <v>52</v>
-      </c>
-      <c r="J48" t="n">
-        <v>3</v>
-      </c>
-      <c r="K48" t="n">
-        <v>1</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-12.03674</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-77.04585</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>3032 VILLA ANGELICA</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-12.0335471</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-77.07082749999999</v>
-      </c>
-      <c r="I49" t="n">
-        <v>807</v>
-      </c>
-      <c r="J49" t="n">
-        <v>38</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-12.0335471</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-77.0708275</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>3033 ANDRES AVELINO CACERES</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-12.03575</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-77.08568</v>
-      </c>
-      <c r="I50" t="n">
-        <v>904</v>
-      </c>
-      <c r="J50" t="n">
-        <v>51</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-12.03575</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-77.08568</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>904</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>3036 JOSE ANDRES RAZURI</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-12.0367</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-77.09050000000001</v>
-      </c>
-      <c r="I51" t="n">
-        <v>325</v>
-      </c>
-      <c r="J51" t="n">
-        <v>17</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-12.0367</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-77.0905</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>3037 GRAN AMAUTA</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-12.0305</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-77.0856</v>
-      </c>
-      <c r="I52" t="n">
-        <v>1789</v>
-      </c>
-      <c r="J52" t="n">
-        <v>94</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-12.0305</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-77.0856</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1789</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>3038 PATRICIA CARMEN GUZMAN</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-12.0272</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-77.08883</v>
-      </c>
-      <c r="I53" t="n">
-        <v>511</v>
-      </c>
-      <c r="J53" t="n">
-        <v>23</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-12.0272</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-77.08883</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>3041 ANDRES BELLO</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-12.02695</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-77.07982</v>
-      </c>
-      <c r="I54" t="n">
-        <v>981</v>
-      </c>
-      <c r="J54" t="n">
-        <v>53</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-12.02695</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-77.07982</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>981</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>3042 JESUS EL SALVADOR</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-12.03108</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-77.06975</v>
-      </c>
-      <c r="I55" t="n">
-        <v>475</v>
-      </c>
-      <c r="J55" t="n">
-        <v>21</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-12.03108</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-77.06975</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>3043 RAMON CASTILLA</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-12.020348</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-77.083476</v>
-      </c>
-      <c r="I56" t="n">
-        <v>1765</v>
-      </c>
-      <c r="J56" t="n">
-        <v>103</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-12.020348</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-77.083476</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1765</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>3044 RICARDO PALMA</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-12.02672</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-77.07093</v>
-      </c>
-      <c r="I57" t="n">
-        <v>351</v>
-      </c>
-      <c r="J57" t="n">
-        <v>19</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-12.02672</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-77.07093</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>3045 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-12.026</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-77.0664</v>
-      </c>
-      <c r="I58" t="n">
-        <v>1279</v>
-      </c>
-      <c r="J58" t="n">
-        <v>67</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-12.026</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-77.0664</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1279</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>3081 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-12.0168</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-77.07513</v>
-      </c>
-      <c r="I59" t="n">
-        <v>1138</v>
-      </c>
-      <c r="J59" t="n">
-        <v>55</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-12.0168</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-77.07513</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1138</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>3093</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-11.96584</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-77.08468999999999</v>
-      </c>
-      <c r="I60" t="n">
-        <v>325</v>
-      </c>
-      <c r="J60" t="n">
-        <v>14</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-11.96584</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-77.08469</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>2073 JOSE OLAYA BALANDRA</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-11.9534</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-77.08629999999999</v>
-      </c>
-      <c r="I61" t="n">
-        <v>841</v>
-      </c>
-      <c r="J61" t="n">
-        <v>34</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-11.9534</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-77.0863</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3641,20 +4229,30 @@
           <t>0051 CLORINDA MATTO DE TURNER</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-12.02618</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-77.05959</v>
-      </c>
-      <c r="I62" t="n">
-        <v>691</v>
-      </c>
-      <c r="J62" t="n">
-        <v>48</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-12.02618</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-77.05959</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3693,20 +4291,30 @@
           <t>EL PACIFICO</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>-12.0021</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-77.0855</v>
-      </c>
-      <c r="I63" t="n">
-        <v>701</v>
-      </c>
-      <c r="J63" t="n">
-        <v>42</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-12.0021</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-77.0855</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3745,20 +4353,30 @@
           <t>ISABEL CHIMPU OCLLO</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>-12.03502</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-77.09341000000001</v>
-      </c>
-      <c r="I64" t="n">
-        <v>710</v>
-      </c>
-      <c r="J64" t="n">
-        <v>70</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-12.03502</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-77.09341</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3797,20 +4415,30 @@
           <t>JOSE HECTOR RODRIGUEZ TRIGOSO</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>-12.01502</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-77.07384</v>
-      </c>
-      <c r="I65" t="n">
-        <v>301</v>
-      </c>
-      <c r="J65" t="n">
-        <v>16</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-12.01502</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-77.07384</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3849,20 +4477,30 @@
           <t>LOS JAZMINES DEL NARANJAL</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>-11.9809</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-77.08750000000001</v>
-      </c>
-      <c r="I66" t="n">
-        <v>1321</v>
-      </c>
-      <c r="J66" t="n">
-        <v>62</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-11.9809</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-77.0875</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3901,20 +4539,30 @@
           <t>2075 NUEVO AMANECER</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>-12.018525</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-77.067375</v>
-      </c>
-      <c r="I67" t="n">
-        <v>340</v>
-      </c>
-      <c r="J67" t="n">
-        <v>20</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-12.018525</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-77.067375</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3953,20 +4601,30 @@
           <t>3082 PARAISO FLORIDO</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>-11.9876</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-77.1014</v>
-      </c>
-      <c r="I68" t="n">
-        <v>614</v>
-      </c>
-      <c r="J68" t="n">
-        <v>32</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-11.9876</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-77.1014</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -4005,20 +4663,30 @@
           <t>CORONEL JUAN VALER SANDOVAL</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>-12.01772</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-77.08153</v>
-      </c>
-      <c r="I69" t="n">
-        <v>418</v>
-      </c>
-      <c r="J69" t="n">
-        <v>19</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-12.01772</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-77.08153</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4057,20 +4725,30 @@
           <t>CESAR VALLEJO MENDOZA</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>-12.03276</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-77.06793999999999</v>
-      </c>
-      <c r="I70" t="n">
-        <v>480</v>
-      </c>
-      <c r="J70" t="n">
-        <v>29</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-12.03276</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-77.06794</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4109,20 +4787,30 @@
           <t>JUAN XXIII</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>-12.01206</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-77.05992999999999</v>
-      </c>
-      <c r="I71" t="n">
-        <v>229</v>
-      </c>
-      <c r="J71" t="n">
-        <v>16</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-12.01206</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-77.05993</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4161,20 +4849,30 @@
           <t>LUIS E. GALVAN</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>-12.03162</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-77.06179</v>
-      </c>
-      <c r="I72" t="n">
-        <v>205</v>
-      </c>
-      <c r="J72" t="n">
-        <v>23</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-12.03162</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-77.06179</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4213,20 +4911,30 @@
           <t>MAGDA PORTAL</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>-12.03106</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-77.09005000000001</v>
-      </c>
-      <c r="I73" t="n">
-        <v>174</v>
-      </c>
-      <c r="J73" t="n">
-        <v>14</v>
-      </c>
-      <c r="K73" t="n">
-        <v>1</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-12.03106</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-77.09005</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4265,20 +4973,30 @@
           <t>NIELS BOHR</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>-11.98623</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-77.09811999999999</v>
-      </c>
-      <c r="I74" t="n">
-        <v>224</v>
-      </c>
-      <c r="J74" t="n">
-        <v>15</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-11.98623</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-77.09812</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4317,20 +5035,30 @@
           <t>RODMAR SCHOOL</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>-12.026833</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-77.05158299999999</v>
-      </c>
-      <c r="I75" t="n">
-        <v>236</v>
-      </c>
-      <c r="J75" t="n">
-        <v>14</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-12.026833</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-77.051583</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4369,20 +5097,30 @@
           <t>NUESTRA SEÑORA DE LA NATIVIDAD</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>-12.03373</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-77.05095</v>
-      </c>
-      <c r="I76" t="n">
-        <v>205</v>
-      </c>
-      <c r="J76" t="n">
-        <v>19</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-12.03373</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-77.05095</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4421,20 +5159,30 @@
           <t>NUESTRA SEÑORA DE LA PAZ</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>-12.0112</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-77.08578</v>
-      </c>
-      <c r="I77" t="n">
-        <v>407</v>
-      </c>
-      <c r="J77" t="n">
-        <v>33</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-12.0112</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-77.08578</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4473,20 +5221,30 @@
           <t>NUESTRA SEÑORA DEL CARMEN DE PALAO</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>-12.01883</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-77.05392000000001</v>
-      </c>
-      <c r="I78" t="n">
-        <v>373</v>
-      </c>
-      <c r="J78" t="n">
-        <v>20</v>
-      </c>
-      <c r="K78" t="n">
-        <v>1</v>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-12.01883</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-77.05392</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4525,20 +5283,30 @@
           <t>REINO DE LOS CIELOS</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>-12.024078</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-77.054689</v>
-      </c>
-      <c r="I79" t="n">
-        <v>268</v>
-      </c>
-      <c r="J79" t="n">
-        <v>25</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-12.024078</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-77.054689</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4577,20 +5345,30 @@
           <t>CAP. FAP JOSE QUIÑONES</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>-12.00107</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-77.08614</v>
-      </c>
-      <c r="I80" t="n">
-        <v>211</v>
-      </c>
-      <c r="J80" t="n">
-        <v>9</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-12.00107</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-77.08614</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4629,20 +5407,30 @@
           <t>SAN ANTONIO DE PADUA</t>
         </is>
       </c>
-      <c r="G81" t="n">
-        <v>-12.01125</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-77.05723</v>
-      </c>
-      <c r="I81" t="n">
-        <v>205</v>
-      </c>
-      <c r="J81" t="n">
-        <v>11</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-12.01125</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-77.05723</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4681,20 +5469,30 @@
           <t>SANTA ANA DE INGENIERIA</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v>-12.02474</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-77.05052000000001</v>
-      </c>
-      <c r="I82" t="n">
-        <v>683</v>
-      </c>
-      <c r="J82" t="n">
-        <v>26</v>
-      </c>
-      <c r="K82" t="n">
-        <v>1</v>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-12.02474</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-77.05052</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4733,20 +5531,30 @@
           <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>-12.02417</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-77.06377000000001</v>
-      </c>
-      <c r="I83" t="n">
-        <v>270</v>
-      </c>
-      <c r="J83" t="n">
-        <v>17</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-12.02417</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-77.06377</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4785,20 +5593,30 @@
           <t>VIRGEN DE GUADALUPE</t>
         </is>
       </c>
-      <c r="G84" t="n">
-        <v>-11.94735</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-77.08795000000001</v>
-      </c>
-      <c r="I84" t="n">
-        <v>258</v>
-      </c>
-      <c r="J84" t="n">
-        <v>15</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-11.94735</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-77.08795</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4837,20 +5655,30 @@
           <t>ARQUITECTOS SCHOOL</t>
         </is>
       </c>
-      <c r="G85" t="n">
-        <v>-12.03543</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-77.08092000000001</v>
-      </c>
-      <c r="I85" t="n">
-        <v>215</v>
-      </c>
-      <c r="J85" t="n">
-        <v>18</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-12.03543</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-77.08092</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4889,20 +5717,30 @@
           <t>EL NUEVO MARIANNE FROSTIG</t>
         </is>
       </c>
-      <c r="G86" t="n">
-        <v>-12.01393</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-77.07531</v>
-      </c>
-      <c r="I86" t="n">
-        <v>388</v>
-      </c>
-      <c r="J86" t="n">
-        <v>21</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-12.01393</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-77.07531</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4941,20 +5779,30 @@
           <t>HARVARD SCHOOL S.M.P.</t>
         </is>
       </c>
-      <c r="G87" t="n">
-        <v>-12.023256</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-77.08093100000001</v>
-      </c>
-      <c r="I87" t="n">
-        <v>65</v>
-      </c>
-      <c r="J87" t="n">
-        <v>9</v>
-      </c>
-      <c r="K87" t="n">
-        <v>1</v>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-12.023256</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-77.080931</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4993,20 +5841,30 @@
           <t>HENRI WALLON</t>
         </is>
       </c>
-      <c r="G88" t="n">
-        <v>-12.02992</v>
-      </c>
-      <c r="H88" t="n">
-        <v>-77.0907</v>
-      </c>
-      <c r="I88" t="n">
-        <v>245</v>
-      </c>
-      <c r="J88" t="n">
-        <v>13</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-12.02992</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-77.0907</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -5045,20 +5903,30 @@
           <t>JUAN PABLO AYLLON HERRERA</t>
         </is>
       </c>
-      <c r="G89" t="n">
-        <v>-12.007768</v>
-      </c>
-      <c r="H89" t="n">
-        <v>-77.08883299999999</v>
-      </c>
-      <c r="I89" t="n">
-        <v>264</v>
-      </c>
-      <c r="J89" t="n">
-        <v>21</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-12.007768</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-77.088833</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -5097,20 +5965,30 @@
           <t>SAN PIO X</t>
         </is>
       </c>
-      <c r="G90" t="n">
-        <v>-12.0257</v>
-      </c>
-      <c r="H90" t="n">
-        <v>-77.0596</v>
-      </c>
-      <c r="I90" t="n">
-        <v>419</v>
-      </c>
-      <c r="J90" t="n">
-        <v>36</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-12.0257</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-77.0596</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -5149,20 +6027,30 @@
           <t>SOCIEDAD EDUCATIVA INGENIERIA SAN SILVESTRE S.A.C.</t>
         </is>
       </c>
-      <c r="G91" t="n">
-        <v>-12.02406</v>
-      </c>
-      <c r="H91" t="n">
-        <v>-77.07499</v>
-      </c>
-      <c r="I91" t="n">
-        <v>151</v>
-      </c>
-      <c r="J91" t="n">
-        <v>8</v>
-      </c>
-      <c r="K91" t="n">
-        <v>1</v>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-12.02406</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-77.07499</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -5201,20 +6089,30 @@
           <t>SANTO TOMAS DE AQUINO DE LOS JARDIN / SANTO TOMAS DE AQUINO DE LOS JARDINES</t>
         </is>
       </c>
-      <c r="G92" t="n">
-        <v>-12.01357</v>
-      </c>
-      <c r="H92" t="n">
-        <v>-77.05473000000001</v>
-      </c>
-      <c r="I92" t="n">
-        <v>571</v>
-      </c>
-      <c r="J92" t="n">
-        <v>28</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-12.01357</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-77.05473</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -5253,20 +6151,30 @@
           <t>HONORES VON BRAUN</t>
         </is>
       </c>
-      <c r="G93" t="n">
-        <v>-11.953417</v>
-      </c>
-      <c r="H93" t="n">
-        <v>-77.09246899999999</v>
-      </c>
-      <c r="I93" t="n">
-        <v>226</v>
-      </c>
-      <c r="J93" t="n">
-        <v>6</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-11.953417</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-77.092469</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -5305,20 +6213,30 @@
           <t>SAN FRANCISCO DE CAYRAN</t>
         </is>
       </c>
-      <c r="G94" t="n">
-        <v>-11.99265</v>
-      </c>
-      <c r="H94" t="n">
-        <v>-77.08474</v>
-      </c>
-      <c r="I94" t="n">
-        <v>439</v>
-      </c>
-      <c r="J94" t="n">
-        <v>22</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0</v>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-11.99265</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-77.08474</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -5357,20 +6275,30 @@
           <t>PERUANO CANADIENSE SAN DIEGO COLLEGE</t>
         </is>
       </c>
-      <c r="G95" t="n">
-        <v>-11.9495</v>
-      </c>
-      <c r="H95" t="n">
-        <v>-77.0911</v>
-      </c>
-      <c r="I95" t="n">
-        <v>320</v>
-      </c>
-      <c r="J95" t="n">
-        <v>14</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-11.9495</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-77.0911</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -5409,20 +6337,30 @@
           <t>PITAGORAS KID'S</t>
         </is>
       </c>
-      <c r="G96" t="n">
-        <v>-12.03262</v>
-      </c>
-      <c r="H96" t="n">
-        <v>-77.07546000000001</v>
-      </c>
-      <c r="I96" t="n">
-        <v>137</v>
-      </c>
-      <c r="J96" t="n">
-        <v>8</v>
-      </c>
-      <c r="K96" t="n">
-        <v>3</v>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-12.03262</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-77.07546</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -5461,20 +6399,30 @@
           <t>2009 FE Y ALEGRIA 2</t>
         </is>
       </c>
-      <c r="G97" t="n">
-        <v>-12.023</v>
-      </c>
-      <c r="H97" t="n">
-        <v>-77.07550000000001</v>
-      </c>
-      <c r="I97" t="n">
-        <v>1479</v>
-      </c>
-      <c r="J97" t="n">
-        <v>67</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-12.023</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-77.0755</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1479</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -5513,20 +6461,30 @@
           <t>ABRAHAM LINCOLN COLLEGE</t>
         </is>
       </c>
-      <c r="G98" t="n">
-        <v>-12.0149</v>
-      </c>
-      <c r="H98" t="n">
-        <v>-77.0761</v>
-      </c>
-      <c r="I98" t="n">
-        <v>456</v>
-      </c>
-      <c r="J98" t="n">
-        <v>26</v>
-      </c>
-      <c r="K98" t="n">
-        <v>0</v>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-12.0149</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-77.0761</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -5565,20 +6523,30 @@
           <t>SANTISIMA VIRGEN DE LA PUERTA</t>
         </is>
       </c>
-      <c r="G99" t="n">
-        <v>-12.00728</v>
-      </c>
-      <c r="H99" t="n">
-        <v>-77.09126000000001</v>
-      </c>
-      <c r="I99" t="n">
-        <v>542</v>
-      </c>
-      <c r="J99" t="n">
-        <v>30</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0</v>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-12.00728</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-77.09126</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -5617,20 +6585,30 @@
           <t>MARTINCITO</t>
         </is>
       </c>
-      <c r="G100" t="n">
-        <v>-12.01639</v>
-      </c>
-      <c r="H100" t="n">
-        <v>-77.05261</v>
-      </c>
-      <c r="I100" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" t="n">
-        <v>1</v>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-12.01639</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-77.05261</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -5669,20 +6647,30 @@
           <t>SAN MIGUEL ARCANGEL</t>
         </is>
       </c>
-      <c r="G101" t="n">
-        <v>-11.960267</v>
-      </c>
-      <c r="H101" t="n">
-        <v>-77.086567</v>
-      </c>
-      <c r="I101" t="n">
-        <v>359</v>
-      </c>
-      <c r="J101" t="n">
-        <v>21</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-11.960267</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-77.086567</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -5721,20 +6709,30 @@
           <t>SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
-      <c r="G102" t="n">
-        <v>-11.99206</v>
-      </c>
-      <c r="H102" t="n">
-        <v>-77.10166</v>
-      </c>
-      <c r="I102" t="n">
-        <v>449</v>
-      </c>
-      <c r="J102" t="n">
-        <v>22</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-11.99206</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-77.10166</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -5773,20 +6771,30 @@
           <t>SAN JOSE DE CLUNY</t>
         </is>
       </c>
-      <c r="G103" t="n">
-        <v>-12.00111</v>
-      </c>
-      <c r="H103" t="n">
-        <v>-77.09302</v>
-      </c>
-      <c r="I103" t="n">
-        <v>355</v>
-      </c>
-      <c r="J103" t="n">
-        <v>23</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0</v>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-12.00111</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-77.09302</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -5825,20 +6833,30 @@
           <t>VIRGEN DE CZESTOCHOWA</t>
         </is>
       </c>
-      <c r="G104" t="n">
-        <v>-12.0312</v>
-      </c>
-      <c r="H104" t="n">
-        <v>-77.07640000000001</v>
-      </c>
-      <c r="I104" t="n">
-        <v>89</v>
-      </c>
-      <c r="J104" t="n">
-        <v>7</v>
-      </c>
-      <c r="K104" t="n">
-        <v>2</v>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-12.0312</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-77.0764</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -5877,20 +6895,30 @@
           <t>MONITOR HUASCAR</t>
         </is>
       </c>
-      <c r="G105" t="n">
-        <v>-11.97989</v>
-      </c>
-      <c r="H105" t="n">
-        <v>-77.09656</v>
-      </c>
-      <c r="I105" t="n">
-        <v>696</v>
-      </c>
-      <c r="J105" t="n">
-        <v>37</v>
-      </c>
-      <c r="K105" t="n">
-        <v>0</v>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-11.97989</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-77.09656</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -5929,20 +6957,30 @@
           <t>MAGDA PORTAL</t>
         </is>
       </c>
-      <c r="G106" t="n">
-        <v>-12.03112</v>
-      </c>
-      <c r="H106" t="n">
-        <v>-77.08909</v>
-      </c>
-      <c r="I106" t="n">
-        <v>16</v>
-      </c>
-      <c r="J106" t="n">
-        <v>2</v>
-      </c>
-      <c r="K106" t="n">
-        <v>1</v>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-12.03112</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-77.08909</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -5981,20 +7019,30 @@
           <t>PABLO PICASSO</t>
         </is>
       </c>
-      <c r="G107" t="n">
-        <v>-12.02293</v>
-      </c>
-      <c r="H107" t="n">
-        <v>-77.06286</v>
-      </c>
-      <c r="I107" t="n">
-        <v>247</v>
-      </c>
-      <c r="J107" t="n">
-        <v>16</v>
-      </c>
-      <c r="K107" t="n">
-        <v>0</v>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-12.02293</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-77.06286</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -6033,20 +7081,30 @@
           <t>LOS DOMINICOS DE PALAO</t>
         </is>
       </c>
-      <c r="G108" t="n">
-        <v>-12.01576</v>
-      </c>
-      <c r="H108" t="n">
-        <v>-77.05589000000001</v>
-      </c>
-      <c r="I108" t="n">
-        <v>325</v>
-      </c>
-      <c r="J108" t="n">
-        <v>18</v>
-      </c>
-      <c r="K108" t="n">
-        <v>0</v>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-12.01576</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-77.05589</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -6085,20 +7143,30 @@
           <t>VILLA AMERICA</t>
         </is>
       </c>
-      <c r="G109" t="n">
-        <v>-11.9954</v>
-      </c>
-      <c r="H109" t="n">
-        <v>-77.0853</v>
-      </c>
-      <c r="I109" t="n">
-        <v>299</v>
-      </c>
-      <c r="J109" t="n">
-        <v>18</v>
-      </c>
-      <c r="K109" t="n">
-        <v>0</v>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-11.9954</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-77.0853</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -6137,20 +7205,30 @@
           <t>LORD BRAIN</t>
         </is>
       </c>
-      <c r="G110" t="n">
-        <v>-11.97131</v>
-      </c>
-      <c r="H110" t="n">
-        <v>-77.09665</v>
-      </c>
-      <c r="I110" t="n">
-        <v>347</v>
-      </c>
-      <c r="J110" t="n">
-        <v>15</v>
-      </c>
-      <c r="K110" t="n">
-        <v>0</v>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-11.97131</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-77.09665</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -6189,20 +7267,30 @@
           <t>LICEO SAN AGUSTIN</t>
         </is>
       </c>
-      <c r="G111" t="n">
-        <v>-11.983133</v>
-      </c>
-      <c r="H111" t="n">
-        <v>-77.094933</v>
-      </c>
-      <c r="I111" t="n">
-        <v>1068</v>
-      </c>
-      <c r="J111" t="n">
-        <v>48</v>
-      </c>
-      <c r="K111" t="n">
-        <v>0</v>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-11.983133</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>-77.094933</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1068</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -6241,20 +7329,30 @@
           <t>FRANCISCA DIEZ CANSECO DE CASTILLA</t>
         </is>
       </c>
-      <c r="G112" t="n">
-        <v>-11.97188</v>
-      </c>
-      <c r="H112" t="n">
-        <v>-77.10039999999999</v>
-      </c>
-      <c r="I112" t="n">
-        <v>334</v>
-      </c>
-      <c r="J112" t="n">
-        <v>15</v>
-      </c>
-      <c r="K112" t="n">
-        <v>0</v>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-11.97188</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-77.1004</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -6293,20 +7391,30 @@
           <t>SANTA ANA DE LOS JARDINES</t>
         </is>
       </c>
-      <c r="G113" t="n">
-        <v>-12.01399</v>
-      </c>
-      <c r="H113" t="n">
-        <v>-77.05519</v>
-      </c>
-      <c r="I113" t="n">
-        <v>744</v>
-      </c>
-      <c r="J113" t="n">
-        <v>23</v>
-      </c>
-      <c r="K113" t="n">
-        <v>0</v>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-12.01399</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>-77.05519</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -6345,20 +7453,30 @@
           <t>TECHNOLOGY SCHOOLS DE SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G114" t="n">
-        <v>-11.99315</v>
-      </c>
-      <c r="H114" t="n">
-        <v>-77.09957</v>
-      </c>
-      <c r="I114" t="n">
-        <v>394</v>
-      </c>
-      <c r="J114" t="n">
-        <v>24</v>
-      </c>
-      <c r="K114" t="n">
-        <v>0</v>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-11.99315</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-77.09957</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -6397,20 +7515,30 @@
           <t>TECHNOLOGY SCHOOLS CAYETANO</t>
         </is>
       </c>
-      <c r="G115" t="n">
-        <v>-12.02445</v>
-      </c>
-      <c r="H115" t="n">
-        <v>-77.05789</v>
-      </c>
-      <c r="I115" t="n">
-        <v>629</v>
-      </c>
-      <c r="J115" t="n">
-        <v>17</v>
-      </c>
-      <c r="K115" t="n">
-        <v>0</v>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-12.02445</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>-77.05789</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -6449,20 +7577,30 @@
           <t>PRIMERA NATURALEZA</t>
         </is>
       </c>
-      <c r="G116" t="n">
-        <v>-12.00397</v>
-      </c>
-      <c r="H116" t="n">
-        <v>-77.08392000000001</v>
-      </c>
-      <c r="I116" t="n">
-        <v>16</v>
-      </c>
-      <c r="J116" t="n">
-        <v>3</v>
-      </c>
-      <c r="K116" t="n">
-        <v>1</v>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-12.00397</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>-77.08392</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -6501,20 +7639,30 @@
           <t>SANTA MARIA PURISIMA</t>
         </is>
       </c>
-      <c r="G117" t="n">
-        <v>-11.96392</v>
-      </c>
-      <c r="H117" t="n">
-        <v>-77.10533</v>
-      </c>
-      <c r="I117" t="n">
-        <v>299</v>
-      </c>
-      <c r="J117" t="n">
-        <v>16</v>
-      </c>
-      <c r="K117" t="n">
-        <v>0</v>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-11.96392</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>-77.10533</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -6553,20 +7701,30 @@
           <t>INGENIERIA DE CONDEVILLA</t>
         </is>
       </c>
-      <c r="G118" t="n">
-        <v>-12.02237</v>
-      </c>
-      <c r="H118" t="n">
-        <v>-77.09025</v>
-      </c>
-      <c r="I118" t="n">
-        <v>362</v>
-      </c>
-      <c r="J118" t="n">
-        <v>15</v>
-      </c>
-      <c r="K118" t="n">
-        <v>0</v>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-12.02237</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>-77.09025</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -6605,20 +7763,30 @@
           <t>SAN MARTIN DE LOS ALGARROBOS</t>
         </is>
       </c>
-      <c r="G119" t="n">
-        <v>-11.97025</v>
-      </c>
-      <c r="H119" t="n">
-        <v>-77.10866</v>
-      </c>
-      <c r="I119" t="n">
-        <v>256</v>
-      </c>
-      <c r="J119" t="n">
-        <v>13</v>
-      </c>
-      <c r="K119" t="n">
-        <v>0</v>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-11.97025</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>-77.10866</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -6657,20 +7825,30 @@
           <t>3035 BELLA LETICIA</t>
         </is>
       </c>
-      <c r="G120" t="n">
-        <v>-12.0341</v>
-      </c>
-      <c r="H120" t="n">
-        <v>-77.062</v>
-      </c>
-      <c r="I120" t="n">
-        <v>490</v>
-      </c>
-      <c r="J120" t="n">
-        <v>27</v>
-      </c>
-      <c r="K120" t="n">
-        <v>0</v>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-12.0341</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-77.062</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -6709,20 +7887,30 @@
           <t>DOMINGO SAVIO DE SAN MARTIN I</t>
         </is>
       </c>
-      <c r="G121" t="n">
-        <v>-12.016194</v>
-      </c>
-      <c r="H121" t="n">
-        <v>-77.083097</v>
-      </c>
-      <c r="I121" t="n">
-        <v>278</v>
-      </c>
-      <c r="J121" t="n">
-        <v>15</v>
-      </c>
-      <c r="K121" t="n">
-        <v>0</v>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-12.016194</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>-77.083097</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -6761,20 +7949,30 @@
           <t>SANTA TERESA DE JESUS - SOPHIANUM</t>
         </is>
       </c>
-      <c r="G122" t="n">
-        <v>-11.996865</v>
-      </c>
-      <c r="H122" t="n">
-        <v>-77.098168</v>
-      </c>
-      <c r="I122" t="n">
-        <v>212</v>
-      </c>
-      <c r="J122" t="n">
-        <v>15</v>
-      </c>
-      <c r="K122" t="n">
-        <v>0</v>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-11.996865</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>-77.098168</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -6813,20 +8011,30 @@
           <t>ANGELITOS DE JESUS EN TRAVESURAS</t>
         </is>
       </c>
-      <c r="G123" t="n">
-        <v>-12.00844</v>
-      </c>
-      <c r="H123" t="n">
-        <v>-77.08286</v>
-      </c>
-      <c r="I123" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" t="n">
-        <v>1</v>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-12.00844</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-77.08286</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -6865,20 +8073,30 @@
           <t>HONORES OQUENDO</t>
         </is>
       </c>
-      <c r="G124" t="n">
-        <v>-11.97957</v>
-      </c>
-      <c r="H124" t="n">
-        <v>-77.11181000000001</v>
-      </c>
-      <c r="I124" t="n">
-        <v>664</v>
-      </c>
-      <c r="J124" t="n">
-        <v>24</v>
-      </c>
-      <c r="K124" t="n">
-        <v>0</v>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-11.97957</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>-77.11181</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -6917,20 +8135,30 @@
           <t>HONORABLE ABRAHAM LINCOLN</t>
         </is>
       </c>
-      <c r="G125" t="n">
-        <v>-11.98266</v>
-      </c>
-      <c r="H125" t="n">
-        <v>-77.10746</v>
-      </c>
-      <c r="I125" t="n">
-        <v>8</v>
-      </c>
-      <c r="J125" t="n">
-        <v>4</v>
-      </c>
-      <c r="K125" t="n">
-        <v>1</v>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-11.98266</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>-77.10746</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -6969,20 +8197,30 @@
           <t>SAN LUIS</t>
         </is>
       </c>
-      <c r="G126" t="n">
-        <v>-12.03431</v>
-      </c>
-      <c r="H126" t="n">
-        <v>-77.08767</v>
-      </c>
-      <c r="I126" t="n">
-        <v>574</v>
-      </c>
-      <c r="J126" t="n">
-        <v>18</v>
-      </c>
-      <c r="K126" t="n">
-        <v>0</v>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-12.03431</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>-77.08767</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -7021,20 +8259,30 @@
           <t>HONORES</t>
         </is>
       </c>
-      <c r="G127" t="n">
-        <v>-11.959931</v>
-      </c>
-      <c r="H127" t="n">
-        <v>-77.097146</v>
-      </c>
-      <c r="I127" t="n">
-        <v>257</v>
-      </c>
-      <c r="J127" t="n">
-        <v>11</v>
-      </c>
-      <c r="K127" t="n">
-        <v>0</v>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-11.959931</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>-77.097146</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -7073,20 +8321,30 @@
           <t>JUAN PABLO PEREGRINO</t>
         </is>
       </c>
-      <c r="G128" t="n">
-        <v>-11.98381</v>
-      </c>
-      <c r="H128" t="n">
-        <v>-77.08954</v>
-      </c>
-      <c r="I128" t="n">
-        <v>362</v>
-      </c>
-      <c r="J128" t="n">
-        <v>21</v>
-      </c>
-      <c r="K128" t="n">
-        <v>0</v>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-11.98381</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>-77.08954</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -7125,20 +8383,30 @@
           <t>SANTA ANA DE INGENIERIA</t>
         </is>
       </c>
-      <c r="G129" t="n">
-        <v>-12.02477</v>
-      </c>
-      <c r="H129" t="n">
-        <v>-77.05112</v>
-      </c>
-      <c r="I129" t="n">
-        <v>169</v>
-      </c>
-      <c r="J129" t="n">
-        <v>9</v>
-      </c>
-      <c r="K129" t="n">
-        <v>1</v>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-12.02477</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>-77.05112</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -7177,20 +8445,30 @@
           <t>INNOVA SCHOOLS - SMP PERU</t>
         </is>
       </c>
-      <c r="G130" t="n">
-        <v>-12.03164</v>
-      </c>
-      <c r="H130" t="n">
-        <v>-77.06005</v>
-      </c>
-      <c r="I130" t="n">
-        <v>872</v>
-      </c>
-      <c r="J130" t="n">
-        <v>29</v>
-      </c>
-      <c r="K130" t="n">
-        <v>0</v>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>-12.03164</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-77.06005</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>872</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -7229,20 +8507,30 @@
           <t>JESUS DIVINO MAESTRO</t>
         </is>
       </c>
-      <c r="G131" t="n">
-        <v>-11.98835</v>
-      </c>
-      <c r="H131" t="n">
-        <v>-77.10532000000001</v>
-      </c>
-      <c r="I131" t="n">
-        <v>168</v>
-      </c>
-      <c r="J131" t="n">
-        <v>10</v>
-      </c>
-      <c r="K131" t="n">
-        <v>1</v>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>-11.98835</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>-77.10532</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -7281,20 +8569,30 @@
           <t>JUAN PABLO PEREGRINO DE LA PAZ</t>
         </is>
       </c>
-      <c r="G132" t="n">
-        <v>-11.97797</v>
-      </c>
-      <c r="H132" t="n">
-        <v>-77.08802</v>
-      </c>
-      <c r="I132" t="n">
-        <v>545</v>
-      </c>
-      <c r="J132" t="n">
-        <v>27</v>
-      </c>
-      <c r="K132" t="n">
-        <v>0</v>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>-11.97797</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>-77.08802</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -7333,20 +8631,30 @@
           <t>SANTISIMA VIRGEN DEL CAMINO</t>
         </is>
       </c>
-      <c r="G133" t="n">
-        <v>-12.0281</v>
-      </c>
-      <c r="H133" t="n">
-        <v>-77.0654</v>
-      </c>
-      <c r="I133" t="n">
-        <v>209</v>
-      </c>
-      <c r="J133" t="n">
-        <v>17</v>
-      </c>
-      <c r="K133" t="n">
-        <v>0</v>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>-12.0281</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>-77.0654</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -7385,20 +8693,30 @@
           <t>2040 JULIO VIZCARRA AYALA</t>
         </is>
       </c>
-      <c r="G134" t="n">
-        <v>-11.9683</v>
-      </c>
-      <c r="H134" t="n">
-        <v>-77.10145</v>
-      </c>
-      <c r="I134" t="n">
-        <v>611</v>
-      </c>
-      <c r="J134" t="n">
-        <v>29</v>
-      </c>
-      <c r="K134" t="n">
-        <v>0</v>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>-11.9683</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>-77.10145</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -7437,20 +8755,30 @@
           <t>SANTO DOMINGO SAVIO DE SAN MARTIN</t>
         </is>
       </c>
-      <c r="G135" t="n">
-        <v>-12.01649</v>
-      </c>
-      <c r="H135" t="n">
-        <v>-77.08320000000001</v>
-      </c>
-      <c r="I135" t="n">
-        <v>376</v>
-      </c>
-      <c r="J135" t="n">
-        <v>20</v>
-      </c>
-      <c r="K135" t="n">
-        <v>0</v>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-12.01649</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>-77.0832</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -7489,20 +8817,30 @@
           <t>2020 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
-      <c r="G136" t="n">
-        <v>-11.993652</v>
-      </c>
-      <c r="H136" t="n">
-        <v>-77.113069</v>
-      </c>
-      <c r="I136" t="n">
-        <v>292</v>
-      </c>
-      <c r="J136" t="n">
-        <v>12</v>
-      </c>
-      <c r="K136" t="n">
-        <v>0</v>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-11.993652</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-77.113069</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -7541,20 +8879,30 @@
           <t>SAN AGUSTIN DE ANTARES</t>
         </is>
       </c>
-      <c r="G137" t="n">
-        <v>-12.009792</v>
-      </c>
-      <c r="H137" t="n">
-        <v>-77.08447</v>
-      </c>
-      <c r="I137" t="n">
-        <v>251</v>
-      </c>
-      <c r="J137" t="n">
-        <v>18</v>
-      </c>
-      <c r="K137" t="n">
-        <v>0</v>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-12.009792</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>-77.08447</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -7593,20 +8941,30 @@
           <t>CADILLO</t>
         </is>
       </c>
-      <c r="G138" t="n">
-        <v>-11.95924</v>
-      </c>
-      <c r="H138" t="n">
-        <v>-77.09929</v>
-      </c>
-      <c r="I138" t="n">
-        <v>468</v>
-      </c>
-      <c r="J138" t="n">
-        <v>17</v>
-      </c>
-      <c r="K138" t="n">
-        <v>0</v>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-11.95924</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-77.09929</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -7645,20 +9003,30 @@
           <t>CHRISTIAN BARNARD COLLEGE</t>
         </is>
       </c>
-      <c r="G139" t="n">
-        <v>-11.965887</v>
-      </c>
-      <c r="H139" t="n">
-        <v>-77.08961499999999</v>
-      </c>
-      <c r="I139" t="n">
-        <v>334</v>
-      </c>
-      <c r="J139" t="n">
-        <v>12</v>
-      </c>
-      <c r="K139" t="n">
-        <v>0</v>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-11.965887</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-77.089615</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -7697,20 +9065,30 @@
           <t>MARIA DE LA ESPERANZA</t>
         </is>
       </c>
-      <c r="G140" t="n">
-        <v>-12.00763</v>
-      </c>
-      <c r="H140" t="n">
-        <v>-77.08324</v>
-      </c>
-      <c r="I140" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" t="n">
-        <v>1</v>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>-12.00763</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-77.08324</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -7749,20 +9127,30 @@
           <t>AMISTAD</t>
         </is>
       </c>
-      <c r="G141" t="n">
-        <v>-11.9868</v>
-      </c>
-      <c r="H141" t="n">
-        <v>-77.10339999999999</v>
-      </c>
-      <c r="I141" t="n">
-        <v>125</v>
-      </c>
-      <c r="J141" t="n">
-        <v>11</v>
-      </c>
-      <c r="K141" t="n">
-        <v>1</v>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>-11.9868</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>-77.1034</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -7801,20 +9189,30 @@
           <t>PALMER SCHOOL</t>
         </is>
       </c>
-      <c r="G142" t="n">
-        <v>-11.95769</v>
-      </c>
-      <c r="H142" t="n">
-        <v>-77.09423</v>
-      </c>
-      <c r="I142" t="n">
-        <v>519</v>
-      </c>
-      <c r="J142" t="n">
-        <v>29</v>
-      </c>
-      <c r="K142" t="n">
-        <v>0</v>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-11.95769</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>-77.09423</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -7853,20 +9251,30 @@
           <t>SEMILLITAS DE IZAGUIRRE DE ARIEL</t>
         </is>
       </c>
-      <c r="G143" t="n">
-        <v>-12.01891</v>
-      </c>
-      <c r="H143" t="n">
-        <v>-77.05549000000001</v>
-      </c>
-      <c r="I143" t="n">
-        <v>29</v>
-      </c>
-      <c r="J143" t="n">
-        <v>3</v>
-      </c>
-      <c r="K143" t="n">
-        <v>2</v>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>-12.01891</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>-77.05549</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -7905,20 +9313,30 @@
           <t>CRISTO MISERICORDIOSO</t>
         </is>
       </c>
-      <c r="G144" t="n">
-        <v>-11.97243</v>
-      </c>
-      <c r="H144" t="n">
-        <v>-77.09636</v>
-      </c>
-      <c r="I144" t="n">
-        <v>399</v>
-      </c>
-      <c r="J144" t="n">
-        <v>18</v>
-      </c>
-      <c r="K144" t="n">
-        <v>0</v>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>-11.97243</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>-77.09636</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -7957,20 +9375,30 @@
           <t>SANTO DOMINGO EL PREDICADOR</t>
         </is>
       </c>
-      <c r="G145" t="n">
-        <v>-11.975037</v>
-      </c>
-      <c r="H145" t="n">
-        <v>-77.09351100000001</v>
-      </c>
-      <c r="I145" t="n">
-        <v>1293</v>
-      </c>
-      <c r="J145" t="n">
-        <v>63</v>
-      </c>
-      <c r="K145" t="n">
-        <v>0</v>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-11.975037</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>-77.093511</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -8009,20 +9437,30 @@
           <t>CESAR VALLEJO</t>
         </is>
       </c>
-      <c r="G146" t="n">
-        <v>-11.9979</v>
-      </c>
-      <c r="H146" t="n">
-        <v>-77.0912</v>
-      </c>
-      <c r="I146" t="n">
-        <v>424</v>
-      </c>
-      <c r="J146" t="n">
-        <v>22</v>
-      </c>
-      <c r="K146" t="n">
-        <v>0</v>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>-11.9979</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>-77.0912</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -8061,20 +9499,30 @@
           <t>3054 VIRGEN DE LAS MERCEDES</t>
         </is>
       </c>
-      <c r="G147" t="n">
-        <v>-11.99143</v>
-      </c>
-      <c r="H147" t="n">
-        <v>-77.10850000000001</v>
-      </c>
-      <c r="I147" t="n">
-        <v>264</v>
-      </c>
-      <c r="J147" t="n">
-        <v>18</v>
-      </c>
-      <c r="K147" t="n">
-        <v>1</v>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>-11.99143</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>-77.1085</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -8113,20 +9561,30 @@
           <t>SEÑOR DE LA MISERICORDIA</t>
         </is>
       </c>
-      <c r="G148" t="n">
-        <v>-12.02663</v>
-      </c>
-      <c r="H148" t="n">
-        <v>-77.05589999999999</v>
-      </c>
-      <c r="I148" t="n">
-        <v>14</v>
-      </c>
-      <c r="J148" t="n">
-        <v>3</v>
-      </c>
-      <c r="K148" t="n">
-        <v>1</v>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>-12.02663</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>-77.0559</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -8165,20 +9623,30 @@
           <t>LOS INGENIEROS DE LOS OLIVOS</t>
         </is>
       </c>
-      <c r="G149" t="n">
-        <v>-11.98885</v>
-      </c>
-      <c r="H149" t="n">
-        <v>-77.08194</v>
-      </c>
-      <c r="I149" t="n">
-        <v>184</v>
-      </c>
-      <c r="J149" t="n">
-        <v>20</v>
-      </c>
-      <c r="K149" t="n">
-        <v>1</v>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-11.98885</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>-77.08194</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -8217,20 +9685,30 @@
           <t>BH SCHOOL S.M.P.</t>
         </is>
       </c>
-      <c r="G150" t="n">
-        <v>-11.97765</v>
-      </c>
-      <c r="H150" t="n">
-        <v>-77.09389</v>
-      </c>
-      <c r="I150" t="n">
-        <v>260</v>
-      </c>
-      <c r="J150" t="n">
-        <v>21</v>
-      </c>
-      <c r="K150" t="n">
-        <v>0</v>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-11.97765</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>-77.09389</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -8269,20 +9747,30 @@
           <t>GENES DE SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G151" t="n">
-        <v>-11.98937</v>
-      </c>
-      <c r="H151" t="n">
-        <v>-77.08944</v>
-      </c>
-      <c r="I151" t="n">
-        <v>826</v>
-      </c>
-      <c r="J151" t="n">
-        <v>31</v>
-      </c>
-      <c r="K151" t="n">
-        <v>0</v>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>-11.98937</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>-77.08944</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -8321,20 +9809,30 @@
           <t>MIS TALENTOS DE SAN MARTIN</t>
         </is>
       </c>
-      <c r="G152" t="n">
-        <v>-12.0324</v>
-      </c>
-      <c r="H152" t="n">
-        <v>-77.0754</v>
-      </c>
-      <c r="I152" t="n">
-        <v>0</v>
-      </c>
-      <c r="J152" t="n">
-        <v>0</v>
-      </c>
-      <c r="K152" t="n">
-        <v>3</v>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>-12.0324</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>-77.0754</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -8373,20 +9871,30 @@
           <t>FREDERICK TAYLOR</t>
         </is>
       </c>
-      <c r="G153" t="n">
-        <v>-12.03561</v>
-      </c>
-      <c r="H153" t="n">
-        <v>-77.08732000000001</v>
-      </c>
-      <c r="I153" t="n">
-        <v>373</v>
-      </c>
-      <c r="J153" t="n">
-        <v>26</v>
-      </c>
-      <c r="K153" t="n">
-        <v>0</v>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>-12.03561</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>-77.08732</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -8425,20 +9933,30 @@
           <t>SANTA ANA DE INGENIERIA 01</t>
         </is>
       </c>
-      <c r="G154" t="n">
-        <v>-12.02537</v>
-      </c>
-      <c r="H154" t="n">
-        <v>-77.05005</v>
-      </c>
-      <c r="I154" t="n">
-        <v>261</v>
-      </c>
-      <c r="J154" t="n">
-        <v>13</v>
-      </c>
-      <c r="K154" t="n">
-        <v>0</v>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-12.02537</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>-77.05005</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -8477,20 +9995,30 @@
           <t>MI PEQUEÑO MUNDO Y LAS ESTRELLITAS</t>
         </is>
       </c>
-      <c r="G155" t="n">
-        <v>-11.99326</v>
-      </c>
-      <c r="H155" t="n">
-        <v>-77.09962</v>
-      </c>
-      <c r="I155" t="n">
-        <v>244</v>
-      </c>
-      <c r="J155" t="n">
-        <v>11</v>
-      </c>
-      <c r="K155" t="n">
-        <v>0</v>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>-11.99326</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>-77.09962</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -8529,20 +10057,30 @@
           <t>INNOVA SCHOOLS - CANTA CALLAO</t>
         </is>
       </c>
-      <c r="G156" t="n">
-        <v>-11.96122</v>
-      </c>
-      <c r="H156" t="n">
-        <v>-77.08584</v>
-      </c>
-      <c r="I156" t="n">
-        <v>1331</v>
-      </c>
-      <c r="J156" t="n">
-        <v>61</v>
-      </c>
-      <c r="K156" t="n">
-        <v>0</v>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-11.96122</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>-77.08584</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>1331</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -8581,20 +10119,30 @@
           <t>SACO OLIVEROS DE NARANJAL</t>
         </is>
       </c>
-      <c r="G157" t="n">
-        <v>-11.97055</v>
-      </c>
-      <c r="H157" t="n">
-        <v>-77.08832</v>
-      </c>
-      <c r="I157" t="n">
-        <v>491</v>
-      </c>
-      <c r="J157" t="n">
-        <v>16</v>
-      </c>
-      <c r="K157" t="n">
-        <v>0</v>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>-11.97055</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>-77.08832</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -8633,20 +10181,30 @@
           <t>SANTA ANA DE INGENIERIA 02</t>
         </is>
       </c>
-      <c r="G158" t="n">
-        <v>-12.02436</v>
-      </c>
-      <c r="H158" t="n">
-        <v>-77.0505</v>
-      </c>
-      <c r="I158" t="n">
-        <v>42</v>
-      </c>
-      <c r="J158" t="n">
-        <v>3</v>
-      </c>
-      <c r="K158" t="n">
-        <v>1</v>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>-12.02436</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>-77.0505</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -8685,20 +10243,30 @@
           <t>SAN FRANCISCO DE CAYRAN</t>
         </is>
       </c>
-      <c r="G159" t="n">
-        <v>-11.992562</v>
-      </c>
-      <c r="H159" t="n">
-        <v>-77.084822</v>
-      </c>
-      <c r="I159" t="n">
-        <v>232</v>
-      </c>
-      <c r="J159" t="n">
-        <v>12</v>
-      </c>
-      <c r="K159" t="n">
-        <v>0</v>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>-11.992562</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>-77.084822</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -8737,20 +10305,30 @@
           <t>SANTA ANA DE LOS JARDINES III</t>
         </is>
       </c>
-      <c r="G160" t="n">
-        <v>-12.01456</v>
-      </c>
-      <c r="H160" t="n">
-        <v>-77.05609</v>
-      </c>
-      <c r="I160" t="n">
-        <v>263</v>
-      </c>
-      <c r="J160" t="n">
-        <v>14</v>
-      </c>
-      <c r="K160" t="n">
-        <v>0</v>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>-12.01456</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>-77.05609</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -8789,20 +10367,30 @@
           <t>HENRI WALLON</t>
         </is>
       </c>
-      <c r="G161" t="n">
-        <v>-12.02962</v>
-      </c>
-      <c r="H161" t="n">
-        <v>-77.09067</v>
-      </c>
-      <c r="I161" t="n">
-        <v>271</v>
-      </c>
-      <c r="J161" t="n">
-        <v>11</v>
-      </c>
-      <c r="K161" t="n">
-        <v>0</v>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>-12.02962</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>-77.09067</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
@@ -8841,20 +10429,30 @@
           <t>SANTA ANA DE LOS JARDINES II</t>
         </is>
       </c>
-      <c r="G162" t="n">
-        <v>-12.01438</v>
-      </c>
-      <c r="H162" t="n">
-        <v>-77.05571</v>
-      </c>
-      <c r="I162" t="n">
-        <v>351</v>
-      </c>
-      <c r="J162" t="n">
-        <v>11</v>
-      </c>
-      <c r="K162" t="n">
-        <v>0</v>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>-12.01438</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>-77.05571</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -8893,20 +10491,30 @@
           <t>MI BUEN JESUS</t>
         </is>
       </c>
-      <c r="G163" t="n">
-        <v>-12.03549</v>
-      </c>
-      <c r="H163" t="n">
-        <v>-77.09314000000001</v>
-      </c>
-      <c r="I163" t="n">
-        <v>206</v>
-      </c>
-      <c r="J163" t="n">
-        <v>31</v>
-      </c>
-      <c r="K163" t="n">
-        <v>0</v>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>-12.03549</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>-77.09314</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -8945,20 +10553,30 @@
           <t>CIENCIAS NEWTON</t>
         </is>
       </c>
-      <c r="G164" t="n">
-        <v>-11.985448</v>
-      </c>
-      <c r="H164" t="n">
-        <v>-77.08697600000001</v>
-      </c>
-      <c r="I164" t="n">
-        <v>763</v>
-      </c>
-      <c r="J164" t="n">
-        <v>27</v>
-      </c>
-      <c r="K164" t="n">
-        <v>1</v>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>-11.985448</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>-77.086976</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>763</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -8997,20 +10615,30 @@
           <t>0003 NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
-      <c r="G165" t="n">
-        <v>-11.9638</v>
-      </c>
-      <c r="H165" t="n">
-        <v>-77.08799999999999</v>
-      </c>
-      <c r="I165" t="n">
-        <v>453</v>
-      </c>
-      <c r="J165" t="n">
-        <v>20</v>
-      </c>
-      <c r="K165" t="n">
-        <v>0</v>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>-11.9638</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>-77.088</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -9049,20 +10677,30 @@
           <t>SAN FRANCISCO SALESIANO</t>
         </is>
       </c>
-      <c r="G166" t="n">
-        <v>-11.988224</v>
-      </c>
-      <c r="H166" t="n">
-        <v>-77.09936399999999</v>
-      </c>
-      <c r="I166" t="n">
-        <v>212</v>
-      </c>
-      <c r="J166" t="n">
-        <v>11</v>
-      </c>
-      <c r="K166" t="n">
-        <v>0</v>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>-11.988224</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>-77.099364</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -9101,20 +10739,30 @@
           <t>CIENCIAS NEWTON</t>
         </is>
       </c>
-      <c r="G167" t="n">
-        <v>-11.985448</v>
-      </c>
-      <c r="H167" t="n">
-        <v>-77.08697600000001</v>
-      </c>
-      <c r="I167" t="n">
-        <v>95</v>
-      </c>
-      <c r="J167" t="n">
-        <v>5</v>
-      </c>
-      <c r="K167" t="n">
-        <v>1</v>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>-11.985448</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>-77.086976</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LIMA-LIMA-SAN_MARTIN_DE_PORRES.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-SAN_MARTIN_DE_PORRES.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>80860</t>
+          <t>336248</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>VANGUARD SCHOOLS</t>
+          <t>MARTINCITO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.01391</t>
+          <t>-12.01639</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.08558</t>
+          <t>-77.05261</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>102169</t>
+          <t>572527</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CARDANO VIETE INGENIEROS</t>
+          <t>ANGELITOS DE JESUS EN TRAVESURAS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-11.99788</t>
+          <t>-12.00844</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.08956</t>
+          <t>-77.08286</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>312313</t>
+          <t>696085</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ANA MARIA RIVIER</t>
+          <t>MARIA DE LA ESPERANZA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.97685</t>
+          <t>-12.00763</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.08641</t>
+          <t>-77.08324</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>313435</t>
+          <t>743421</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>EL NAZARENO</t>
+          <t>MIS TALENTOS DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-11.9633</t>
+          <t>-12.0324</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.0922</t>
+          <t>-77.0754</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>332655</t>
+          <t>332716</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0005</t>
+          <t>0020</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.94575</t>
+          <t>-11.99628</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.08906</t>
+          <t>-77.09407</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>202</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>332684</t>
+          <t>694656</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0011 SAGRADO CORAZON DE JESUS</t>
+          <t>JESUS DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.02932</t>
+          <t>-11.98835</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.06947</t>
+          <t>-77.10532</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>168</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>332716</t>
+          <t>333424</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>3043 RAMON CASTILLA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.99628</t>
+          <t>-12.020348</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.09407</t>
+          <t>-77.083476</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>103</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>332721</t>
+          <t>102169</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0057</t>
+          <t>CARDANO VIETE INGENIEROS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.03451</t>
+          <t>-11.99788</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.05563</t>
+          <t>-77.08956</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>545</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>332735</t>
+          <t>332684</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0065</t>
+          <t>0011 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.02645</t>
+          <t>-12.02932</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.06532</t>
+          <t>-77.06947</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>247</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>332740</t>
+          <t>332759</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0081 LA SONRISA DE DIOS</t>
+          <t>0313</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.019886</t>
+          <t>-12.0364</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.086935</t>
+          <t>-77.0878</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>243</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,27 +1121,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>332759</t>
+          <t>332764</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0313</t>
+          <t>338 MANITOS CREATIVAS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.0364</t>
+          <t>-12.02541</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.0878</t>
+          <t>-77.08014</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>230</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1183,27 +1183,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>332764</t>
+          <t>332839</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>338 MANITOS CREATIVAS</t>
+          <t>0361</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.02541</t>
+          <t>-12.02818</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.08014</t>
+          <t>-77.09079</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>208</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>332783</t>
+          <t>332900</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0347 LUIS ENRIQUE XII</t>
+          <t>LUIS ENRIQUE XIX</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-11.97135</t>
+          <t>-12.01774</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.10592</t>
+          <t>-77.07859</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>227</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>332815</t>
+          <t>334635</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0358 NIÑO JESUS DE PRAGA</t>
+          <t>SAN ANTONIO DE PADUA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.00635</t>
+          <t>-12.01125</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.09065</t>
+          <t>-77.05723</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>205</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,27 +1369,27 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>332839</t>
+          <t>617984</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0361</t>
+          <t>HONORES</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.02818</t>
+          <t>-11.959931</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.09079</t>
+          <t>-77.097146</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>257</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1431,37 +1431,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>332844</t>
+          <t>696170</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2088 REPUBLICA FEDERAL DE ALEMANIA</t>
+          <t>AMISTAD</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-11.95678</t>
+          <t>-11.9868</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.10062</t>
+          <t>-77.1034</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>125</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>332863</t>
+          <t>754495</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0387 NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>MI PEQUEÑO MUNDO Y LAS ESTRELLITAS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.0062</t>
+          <t>-11.99326</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.08523</t>
+          <t>-77.09962</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>244</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>332882</t>
+          <t>807026</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CONDEVILLA SEÑOR I</t>
+          <t>HENRI WALLON</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.0214</t>
+          <t>-12.02962</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.0814</t>
+          <t>-77.09067</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>271</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>332896</t>
+          <t>807111</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CONDEVILLA SEÑOR II</t>
+          <t>SANTA ANA DE LOS JARDINES II</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.0243</t>
+          <t>-12.01438</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.0735</t>
+          <t>-77.05571</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>351</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,27 +1679,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>849125</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>LUIS ENRIQUE XIX</t>
+          <t>SAN FRANCISCO SALESIANO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.01774</t>
+          <t>-11.988224</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.07859</t>
+          <t>-77.099364</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>212</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>332924</t>
+          <t>332976</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2001 SANTA ROSA DE LIMA</t>
+          <t>2010 ALBERT EINSTEIN</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-11.94492</t>
+          <t>-12.017275</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.08871</t>
+          <t>-77.087375</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>455</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>332938</t>
+          <t>695340</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2002 VIRGEN MARIA DEL ROSARIO</t>
+          <t>2020 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-11.966955</t>
+          <t>-11.993652</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.087685</t>
+          <t>-77.113069</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>292</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>332943</t>
+          <t>696033</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2003 LIBERTADOR JOSE DE SAN MARTIN</t>
+          <t>CHRISTIAN BARNARD COLLEGE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.0063</t>
+          <t>-11.965887</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.091</t>
+          <t>-77.089615</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>334</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>332957</t>
+          <t>802340</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2008 EL ROSARIO</t>
+          <t>SAN FRANCISCO DE CAYRAN</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.02069</t>
+          <t>-11.992562</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.07389</t>
+          <t>-77.084822</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>232</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>332962</t>
+          <t>332740</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2074 VIRGEN PEREGRINA DEL ROSARIO</t>
+          <t>0081 LA SONRISA DE DIOS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-11.97756</t>
+          <t>-12.019886</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.08883</t>
+          <t>-77.086935</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>258</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>332976</t>
+          <t>335220</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2010 ALBERT EINSTEIN</t>
+          <t>HENRI WALLON</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.017275</t>
+          <t>-12.02992</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.087375</t>
+          <t>-77.0907</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>245</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>332995</t>
+          <t>526229</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>SAN MARTIN DE LOS ALGARROBOS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.0177</t>
+          <t>-11.97025</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.062</t>
+          <t>-77.10866</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>256</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>333004</t>
+          <t>752024</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>SANTA ANA DE INGENIERIA 01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.03451</t>
+          <t>-12.02537</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.05606</t>
+          <t>-77.05005</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>261</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,27 +2237,27 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>333018</t>
+          <t>333004</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2014 LOS CHASQUIS</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-11.993831</t>
+          <t>-12.03451</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.097146</t>
+          <t>-77.05606</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>327</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>333075</t>
+          <t>333018</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026 SAN DIEGO</t>
+          <t>2014 LOS CHASQUIS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-11.94765</t>
+          <t>-11.993831</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.093</t>
+          <t>-77.097146</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>346</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>333080</t>
+          <t>333481</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2027 JOSE MARIA ARGUEDAS</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.0158</t>
+          <t>-11.96584</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.05705</t>
+          <t>-77.08469</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>325</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2423,37 +2423,37 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>333103</t>
+          <t>334225</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2029 SIMON BOLIVAR</t>
+          <t>MAGDA PORTAL</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.027</t>
+          <t>-12.03106</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-77.0667</t>
+          <t>-77.09005</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>174</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>333117</t>
+          <t>334428</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2030 VIRGEN DEL CARMEN</t>
+          <t>RODMAR SCHOOL</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.00012</t>
+          <t>-12.026833</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.08946</t>
+          <t>-77.051583</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>236</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>333122</t>
+          <t>335951</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2031 VIRGEN DE FATIMA</t>
+          <t>PERUANO CANADIENSE SAN DIEGO COLLEGE</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-11.98794</t>
+          <t>-11.9495</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-77.09218</t>
+          <t>-77.0911</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>320</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>333141</t>
+          <t>806084</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2033 CARLOS HIRAOKA TORRES</t>
+          <t>SANTA ANA DE LOS JARDINES III</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-11.98562</t>
+          <t>-12.01456</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-77.09974</t>
+          <t>-77.05609</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>263</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>333155</t>
+          <t>332655</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2034 VIRGEN DE FATIMA</t>
+          <t>0005</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.0115</t>
+          <t>-11.94575</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-77.05794</t>
+          <t>-77.08906</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>317</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>333179</t>
+          <t>334409</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2072 MARIO VARGAS LLOSA</t>
+          <t>NIELS BOHR</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-11.9982</t>
+          <t>-11.98623</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-77.0954</t>
+          <t>-77.09812</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>224</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>333198</t>
+          <t>334999</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2082 HEROES DEL PACIFICO</t>
+          <t>VIRGEN DE GUADALUPE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.00299</t>
+          <t>-11.94735</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-77.08484</t>
+          <t>-77.08795</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>258</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>333202</t>
+          <t>336903</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>LOS ALISOS</t>
+          <t>LORD BRAIN</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-11.9848</t>
+          <t>-11.97131</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-77.087875</t>
+          <t>-77.09665</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>347</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>333221</t>
+          <t>336955</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2094 INCA PACHACUTEC</t>
+          <t>FRANCISCA DIEZ CANSECO DE CASTILLA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.02112</t>
+          <t>-11.97188</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-77.0788</t>
+          <t>-77.1004</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>334</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>333235</t>
+          <t>525121</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2098 CABO JESUS VERA FERNANDEZ</t>
+          <t>INGENIERIA DE CONDEVILLA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.01285</t>
+          <t>-12.02237</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-77.06808</t>
+          <t>-77.09025</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>362</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,37 +3043,37 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>333240</t>
+          <t>537218</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2101 MARIA AUXILIADORA</t>
+          <t>DOMINGO SAVIO DE SAN MARTIN I</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.0158</t>
+          <t>-12.016194</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-77.0777</t>
+          <t>-77.083097</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>278</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>333259</t>
+          <t>570726</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>3022 JOSE SABOGAL</t>
+          <t>SANTA TERESA DE JESUS - SOPHIANUM</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.03185</t>
+          <t>-11.996865</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-77.04596</t>
+          <t>-77.098168</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>212</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>333264</t>
+          <t>332735</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>3023 PEDRO E. PAULET MOSTAJO</t>
+          <t>0065</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.0277</t>
+          <t>-12.02645</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-77.0576</t>
+          <t>-77.06532</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>345</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>333283</t>
+          <t>332882</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>3027 CORONEL JOSE BALTA</t>
+          <t>CONDEVILLA SEÑOR I</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.03106</t>
+          <t>-12.0214</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-77.05296</t>
+          <t>-77.0814</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>308</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3353,37 +3353,37 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>333315</t>
+          <t>333589</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>3031 GRANDES TALENTOS</t>
+          <t>JOSE HECTOR RODRIGUEZ TRIGOSO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-12.03674</t>
+          <t>-12.01502</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-77.04585</t>
+          <t>-77.07384</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>301</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>333320</t>
+          <t>334065</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>3032 VILLA ANGELICA</t>
+          <t>JUAN XXIII</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.0335471</t>
+          <t>-12.01206</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-77.0708275</t>
+          <t>-77.05993</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>229</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>333339</t>
+          <t>336644</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>3033 ANDRES AVELINO CACERES</t>
+          <t>PABLO PICASSO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.03575</t>
+          <t>-12.02293</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-77.08568</t>
+          <t>-77.06286</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>247</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>333363</t>
+          <t>512208</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>3036 JOSE ANDRES RAZURI</t>
+          <t>SANTA MARIA PURISIMA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-12.0367</t>
+          <t>-11.96392</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-77.0905</t>
+          <t>-77.10533</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>299</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>333377</t>
+          <t>783695</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>3037 GRAN AMAUTA</t>
+          <t>SACO OLIVEROS DE NARANJAL</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-12.0305</t>
+          <t>-11.97055</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-77.0856</t>
+          <t>-77.08832</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>491</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>333382</t>
+          <t>332721</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>3038 PATRICIA CARMEN GUZMAN</t>
+          <t>0057</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-12.0272</t>
+          <t>-12.03451</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-77.08883</t>
+          <t>-77.05563</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>347</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>333400</t>
+          <t>333235</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>3041 ANDRES BELLO</t>
+          <t>2098 CABO JESUS VERA FERNANDEZ</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-12.02695</t>
+          <t>-12.01285</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-77.07982</t>
+          <t>-77.06808</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>282</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>333419</t>
+          <t>333363</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>3042 JESUS EL SALVADOR</t>
+          <t>3036 JOSE ANDRES RAZURI</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-12.03108</t>
+          <t>-12.0367</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-77.06975</t>
+          <t>-77.0905</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>325</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>333424</t>
+          <t>334895</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>3043 RAMON CASTILLA</t>
+          <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-12.020348</t>
+          <t>-12.02417</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-77.083476</t>
+          <t>-77.06377</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>270</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>333438</t>
+          <t>504760</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>3044 RICARDO PALMA</t>
+          <t>TECHNOLOGY SCHOOLS CAYETANO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-12.02672</t>
+          <t>-12.02445</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-77.07093</t>
+          <t>-77.05789</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>629</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>333443</t>
+          <t>694784</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>3045 JOSE CARLOS MARIATEGUI</t>
+          <t>SANTISIMA VIRGEN DEL CAMINO</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-12.026</t>
+          <t>-12.0281</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-77.0664</t>
+          <t>-77.0654</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>209</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>333462</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>3081 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
+          <t>CADILLO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-12.0168</t>
+          <t>-11.95924</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-77.07513</t>
+          <t>-77.09929</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>468</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>333481</t>
+          <t>332863</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>0387 NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-11.96584</t>
+          <t>-12.0062</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-77.08469</t>
+          <t>-77.08523</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>392</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>333532</t>
+          <t>335102</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2073 JOSE OLAYA BALANDRA</t>
+          <t>ARQUITECTOS SCHOOL</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-11.9534</t>
+          <t>-12.03543</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-77.0863</t>
+          <t>-77.08092</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>215</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>333551</t>
+          <t>336677</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>0051 CLORINDA MATTO DE TURNER</t>
+          <t>LOS DOMINICOS DE PALAO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-12.02618</t>
+          <t>-12.01576</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-77.05959</t>
+          <t>-77.05589</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>325</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>333565</t>
+          <t>336738</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>EL PACIFICO</t>
+          <t>VILLA AMERICA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-12.0021</t>
+          <t>-11.9954</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-77.0855</t>
+          <t>-77.0853</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>299</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>333570</t>
+          <t>604081</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ISABEL CHIMPU OCLLO</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-12.03502</t>
+          <t>-12.03431</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-77.09341</t>
+          <t>-77.08767</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>574</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>333589</t>
+          <t>695646</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>JOSE HECTOR RODRIGUEZ TRIGOSO</t>
+          <t>SAN AGUSTIN DE ANTARES</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-12.01502</t>
+          <t>-12.009792</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-77.07384</t>
+          <t>-77.08447</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>251</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>333594</t>
+          <t>697565</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>LOS JAZMINES DEL NARANJAL</t>
+          <t>CRISTO MISERICORDIOSO</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-11.9809</t>
+          <t>-11.97243</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-77.0875</t>
+          <t>-77.09636</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>399</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4531,37 +4531,37 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>333650</t>
+          <t>697872</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2075 NUEVO AMANECER</t>
+          <t>3054 VIRGEN DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-12.018525</t>
+          <t>-11.99143</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-77.067375</t>
+          <t>-77.1085</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>264</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>333674</t>
+          <t>333438</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>3082 PARAISO FLORIDO</t>
+          <t>3044 RICARDO PALMA</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-11.9876</t>
+          <t>-12.02672</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-77.1014</t>
+          <t>-77.07093</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>351</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>333749</t>
+          <t>334452</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO MENDOZA</t>
+          <t>NUESTRA SEÑORA DE LA NATIVIDAD</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-12.03276</t>
+          <t>-12.03373</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-77.06794</t>
+          <t>-77.05095</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>205</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4779,37 +4779,37 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>334065</t>
+          <t>336564</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>JUAN XXIII</t>
+          <t>MAGDA PORTAL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-12.01206</t>
+          <t>-12.03112</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-77.05993</t>
+          <t>-77.08909</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>334206</t>
+          <t>333117</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>LUIS E. GALVAN</t>
+          <t>2030 VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-12.03162</t>
+          <t>-12.00012</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-77.06179</t>
+          <t>-77.08946</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>455</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4903,37 +4903,37 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>334225</t>
+          <t>333650</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MAGDA PORTAL</t>
+          <t>2075 NUEVO AMANECER</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-12.03106</t>
+          <t>-12.018525</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-77.09005</t>
+          <t>-77.067375</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>340</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4965,37 +4965,37 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>334409</t>
+          <t>334471</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>NIELS BOHR</t>
+          <t>NUESTRA SEÑORA DEL CARMEN DE PALAO</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-11.98623</t>
+          <t>-12.01883</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-77.09812</t>
+          <t>-77.05392</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>373</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>334428</t>
+          <t>695118</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RODMAR SCHOOL</t>
+          <t>SANTO DOMINGO SAVIO DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-12.026833</t>
+          <t>-12.01649</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-77.051583</t>
+          <t>-77.0832</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>376</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5089,37 +5089,37 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>334452</t>
+          <t>698942</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA NATIVIDAD</t>
+          <t>LOS INGENIEROS DE LOS OLIVOS</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-12.03373</t>
+          <t>-11.98885</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-77.05095</t>
+          <t>-77.08194</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>184</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>334466</t>
+          <t>839008</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA PAZ</t>
+          <t>0003 NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-12.0112</t>
+          <t>-11.9638</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-77.08578</t>
+          <t>-77.088</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>453</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5213,37 +5213,37 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>334471</t>
+          <t>333202</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL CARMEN DE PALAO</t>
+          <t>LOS ALISOS</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-12.01883</t>
+          <t>-11.9848</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-77.05392</t>
+          <t>-77.087875</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>492</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>334555</t>
+          <t>333419</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>REINO DE LOS CIELOS</t>
+          <t>3042 JESUS EL SALVADOR</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-12.024078</t>
+          <t>-12.03108</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-77.054689</t>
+          <t>-77.06975</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>475</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>334560</t>
+          <t>335178</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CAP. FAP JOSE QUIÑONES</t>
+          <t>EL NUEVO MARIANNE FROSTIG</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-12.00107</t>
+          <t>-12.01393</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-77.08614</t>
+          <t>-77.07531</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>388</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>334635</t>
+          <t>335338</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SAN ANTONIO DE PADUA</t>
+          <t>JUAN PABLO AYLLON HERRERA</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-12.01125</t>
+          <t>-12.007768</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-77.05723</t>
+          <t>-77.088833</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>264</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5461,37 +5461,37 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>334763</t>
+          <t>336253</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SANTA ANA DE INGENIERIA</t>
+          <t>SAN MIGUEL ARCANGEL</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-12.02474</t>
+          <t>-11.960267</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-77.05052</t>
+          <t>-77.086567</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>359</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>334895</t>
+          <t>619643</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
+          <t>JUAN PABLO PEREGRINO</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-12.02417</t>
+          <t>-11.98381</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-77.06377</t>
+          <t>-77.08954</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>362</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>334999</t>
+          <t>723319</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>VIRGEN DE GUADALUPE</t>
+          <t>BH SCHOOL S.M.P.</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-11.94735</t>
+          <t>-11.97765</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-77.08795</t>
+          <t>-77.09389</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>260</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>335102</t>
+          <t>332957</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ARQUITECTOS SCHOOL</t>
+          <t>2008 EL ROSARIO</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-12.03543</t>
+          <t>-12.02069</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-77.08092</t>
+          <t>-77.07389</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>484</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>335178</t>
+          <t>333155</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>EL NUEVO MARIANNE FROSTIG</t>
+          <t>2034 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-12.01393</t>
+          <t>-12.0115</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-77.07531</t>
+          <t>-77.05794</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>465</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5771,37 +5771,37 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>335201</t>
+          <t>335932</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>HARVARD SCHOOL S.M.P.</t>
+          <t>SAN FRANCISCO DE CAYRAN</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-12.023256</t>
+          <t>-11.99265</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-77.080931</t>
+          <t>-77.08474</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>439</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>335220</t>
+          <t>336328</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>HENRI WALLON</t>
+          <t>SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-12.02992</t>
+          <t>-11.99206</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-77.0907</t>
+          <t>-77.10166</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>449</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>335338</t>
+          <t>697805</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>JUAN PABLO AYLLON HERRERA</t>
+          <t>CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-12.007768</t>
+          <t>-11.9979</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-77.088833</t>
+          <t>-77.0912</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>424</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>335545</t>
+          <t>80860</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SAN PIO X</t>
+          <t>VANGUARD SCHOOLS</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-12.0257</t>
+          <t>-12.01391</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-77.0596</t>
+          <t>-77.08558</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>403</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6019,37 +6019,37 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>335687</t>
+          <t>333179</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>SOCIEDAD EDUCATIVA INGENIERIA SAN SILVESTRE S.A.C.</t>
+          <t>2072 MARIO VARGAS LLOSA</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-12.02406</t>
+          <t>-11.9982</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-77.07499</t>
+          <t>-77.0954</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>595</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6081,32 +6081,32 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>335852</t>
+          <t>333382</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>SANTO TOMAS DE AQUINO DE LOS JARDIN / SANTO TOMAS DE AQUINO DE LOS JARDINES</t>
+          <t>3038 PATRICIA CARMEN GUZMAN</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-12.01357</t>
+          <t>-12.0272</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-77.05473</t>
+          <t>-77.08883</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>511</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6143,32 +6143,32 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>335908</t>
+          <t>334206</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>HONORES VON BRAUN</t>
+          <t>LUIS E. GALVAN</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-11.953417</t>
+          <t>-12.03162</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-77.092469</t>
+          <t>-77.06179</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>205</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6205,32 +6205,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>335932</t>
+          <t>336371</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE CAYRAN</t>
+          <t>SAN JOSE DE CLUNY</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-11.99265</t>
+          <t>-12.00111</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-77.08474</t>
+          <t>-77.09302</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>355</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>335951</t>
+          <t>337281</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>PERUANO CANADIENSE SAN DIEGO COLLEGE</t>
+          <t>SANTA ANA DE LOS JARDINES</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-11.9495</t>
+          <t>-12.01399</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-77.0911</t>
+          <t>-77.05519</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>744</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6329,37 +6329,37 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>335965</t>
+          <t>312313</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>PITAGORAS KID'S</t>
+          <t>ANA MARIA RIVIER</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-12.03262</t>
+          <t>-11.97685</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-77.07546</t>
+          <t>-77.08641</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>203</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>336111</t>
+          <t>332815</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2009 FE Y ALEGRIA 2</t>
+          <t>0358 NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-12.023</t>
+          <t>-12.00635</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-77.0755</t>
+          <t>-77.09065</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>454</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>336229</t>
+          <t>332896</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>ABRAHAM LINCOLN COLLEGE</t>
+          <t>CONDEVILLA SEÑOR II</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-12.0149</t>
+          <t>-12.0243</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-77.0761</t>
+          <t>-77.0735</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>317</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6515,37 +6515,37 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>336234</t>
+          <t>333240</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SANTISIMA VIRGEN DE LA PUERTA</t>
+          <t>2101 MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-12.00728</t>
+          <t>-12.0158</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-77.09126</t>
+          <t>-77.0777</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>517</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6577,37 +6577,37 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>336248</t>
+          <t>337356</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>MARTINCITO</t>
+          <t>TECHNOLOGY SCHOOLS DE SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-12.01639</t>
+          <t>-11.99315</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>-77.05261</t>
+          <t>-77.09957</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>394</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>336253</t>
+          <t>594591</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SAN MIGUEL ARCANGEL</t>
+          <t>HONORES OQUENDO</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-11.960267</t>
+          <t>-11.97957</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>-77.086567</t>
+          <t>-77.11181</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>664</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6701,32 +6701,32 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>336328</t>
+          <t>332995</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DE LOYOLA</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-11.99206</t>
+          <t>-12.0177</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-77.10166</t>
+          <t>-77.062</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>490</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6763,32 +6763,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>336371</t>
+          <t>333141</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>SAN JOSE DE CLUNY</t>
+          <t>2033 CARLOS HIRAOKA TORRES</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-12.00111</t>
+          <t>-11.98562</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-77.09302</t>
+          <t>-77.09974</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>542</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6825,37 +6825,37 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>336432</t>
+          <t>334555</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>VIRGEN DE CZESTOCHOWA</t>
+          <t>REINO DE LOS CIELOS</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-12.0312</t>
+          <t>-12.024078</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>-77.0764</t>
+          <t>-77.054689</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>268</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6887,42 +6887,42 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>336516</t>
+          <t>334763</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>MONITOR HUASCAR</t>
+          <t>SANTA ANA DE INGENIERIA</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-11.97989</t>
+          <t>-12.02474</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>-77.09656</t>
+          <t>-77.05052</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>683</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6949,37 +6949,37 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>336564</t>
+          <t>336229</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>MAGDA PORTAL</t>
+          <t>ABRAHAM LINCOLN COLLEGE</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-12.03112</t>
+          <t>-12.0149</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>-77.08909</t>
+          <t>-77.0761</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>456</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7011,32 +7011,32 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>336644</t>
+          <t>747848</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>PABLO PICASSO</t>
+          <t>FREDERICK TAYLOR</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-12.02293</t>
+          <t>-12.03561</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>-77.06286</t>
+          <t>-77.08732</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>373</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7073,32 +7073,32 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>336677</t>
+          <t>526328</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>LOS DOMINICOS DE PALAO</t>
+          <t>3035 BELLA LETICIA</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-12.01576</t>
+          <t>-12.0341</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>-77.05589</t>
+          <t>-77.062</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>490</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -7135,32 +7135,32 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>336738</t>
+          <t>694675</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>VILLA AMERICA</t>
+          <t>JUAN PABLO PEREGRINO DE LA PAZ</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-11.9954</t>
+          <t>-11.97797</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>-77.0853</t>
+          <t>-77.08802</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>545</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7197,42 +7197,42 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>336903</t>
+          <t>838947</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>LORD BRAIN</t>
+          <t>CIENCIAS NEWTON</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-11.97131</t>
+          <t>-11.985448</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>-77.09665</t>
+          <t>-77.086976</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>763</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7259,32 +7259,32 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>336917</t>
+          <t>335852</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>LICEO SAN AGUSTIN</t>
+          <t>SANTO TOMAS DE AQUINO DE LOS JARDIN / SANTO TOMAS DE AQUINO DE LOS JARDINES</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-11.983133</t>
+          <t>-12.01357</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>-77.094933</t>
+          <t>-77.05473</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>571</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7321,32 +7321,32 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>336955</t>
+          <t>333198</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>FRANCISCA DIEZ CANSECO DE CASTILLA</t>
+          <t>2082 HEROES DEL PACIFICO</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-11.97188</t>
+          <t>-12.00299</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>-77.1004</t>
+          <t>-77.08484</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>570</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7383,32 +7383,32 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>337281</t>
+          <t>333749</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>SANTA ANA DE LOS JARDINES</t>
+          <t>CESAR VALLEJO MENDOZA</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-12.01399</t>
+          <t>-12.03276</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>-77.05519</t>
+          <t>-77.06794</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>480</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7445,32 +7445,32 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>337356</t>
+          <t>649744</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>TECHNOLOGY SCHOOLS DE SAN MARTIN DE PORRES</t>
+          <t>INNOVA SCHOOLS - SMP PERU</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-11.99315</t>
+          <t>-12.03164</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>-77.09957</t>
+          <t>-77.06005</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>872</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7507,32 +7507,32 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>504760</t>
+          <t>694901</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>TECHNOLOGY SCHOOLS CAYETANO</t>
+          <t>2040 JULIO VIZCARRA AYALA</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-12.02445</t>
+          <t>-11.9683</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>-77.05789</t>
+          <t>-77.10145</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>611</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -7569,37 +7569,37 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>506735</t>
+          <t>696448</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>PRIMERA NATURALEZA</t>
+          <t>PALMER SCHOOL</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-12.00397</t>
+          <t>-11.95769</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>-77.08392</t>
+          <t>-77.09423</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>519</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7631,37 +7631,37 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>512208</t>
+          <t>333315</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>SANTA MARIA PURISIMA</t>
+          <t>3031 GRANDES TALENTOS</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-11.96392</t>
+          <t>-12.03674</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>-77.10533</t>
+          <t>-77.04585</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7693,37 +7693,37 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>525121</t>
+          <t>506735</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>INGENIERIA DE CONDEVILLA</t>
+          <t>PRIMERA NATURALEZA</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-12.02237</t>
+          <t>-12.00397</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>-77.09025</t>
+          <t>-77.08392</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7755,37 +7755,37 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>526229</t>
+          <t>696504</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SAN MARTIN DE LOS ALGARROBOS</t>
+          <t>SEMILLITAS DE IZAGUIRRE DE ARIEL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-11.97025</t>
+          <t>-12.01891</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>-77.10866</t>
+          <t>-77.05549</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7817,37 +7817,37 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>526328</t>
+          <t>698678</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>3035 BELLA LETICIA</t>
+          <t>SEÑOR DE LA MISERICORDIA</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-12.0341</t>
+          <t>-12.02663</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>-77.062</t>
+          <t>-77.0559</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7879,37 +7879,37 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>537218</t>
+          <t>801699</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>DOMINGO SAVIO DE SAN MARTIN I</t>
+          <t>SANTA ANA DE INGENIERIA 02</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-12.016194</t>
+          <t>-12.02436</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>-77.083097</t>
+          <t>-77.0505</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7941,37 +7941,37 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>570726</t>
+          <t>313435</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>SANTA TERESA DE JESUS - SOPHIANUM</t>
+          <t>EL NAZARENO</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-11.996865</t>
+          <t>-11.9633</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>-77.098168</t>
+          <t>-77.0922</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>703</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8003,37 +8003,37 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>572527</t>
+          <t>336234</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>ANGELITOS DE JESUS EN TRAVESURAS</t>
+          <t>SANTISIMA VIRGEN DE LA PUERTA</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-12.00844</t>
+          <t>-12.00728</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>-77.08286</t>
+          <t>-77.09126</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>542</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8065,32 +8065,32 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>594591</t>
+          <t>727666</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>HONORES OQUENDO</t>
+          <t>GENES DE SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-11.97957</t>
+          <t>-11.98937</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>-77.11181</t>
+          <t>-77.08944</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>826</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8127,37 +8127,37 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>596024</t>
+          <t>834765</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>HONORABLE ABRAHAM LINCOLN</t>
+          <t>MI BUEN JESUS</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-11.98266</t>
+          <t>-12.03549</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>-77.10746</t>
+          <t>-77.09314</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>206</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8189,32 +8189,32 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>604081</t>
+          <t>333674</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>3082 PARAISO FLORIDO</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-12.03431</t>
+          <t>-11.9876</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>-77.08767</t>
+          <t>-77.1014</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>614</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -8251,32 +8251,32 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>617984</t>
+          <t>333283</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>HONORES</t>
+          <t>3027 CORONEL JOSE BALTA</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>-11.959931</t>
+          <t>-12.03106</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>-77.097146</t>
+          <t>-77.05296</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>403</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8313,32 +8313,32 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>619643</t>
+          <t>334466</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>JUAN PABLO PEREGRINO</t>
+          <t>NUESTRA SEÑORA DE LA PAZ</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>-11.98381</t>
+          <t>-12.0112</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>-77.08954</t>
+          <t>-77.08578</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>407</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -8375,37 +8375,37 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>640164</t>
+          <t>333532</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>SANTA ANA DE INGENIERIA</t>
+          <t>2073 JOSE OLAYA BALANDRA</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>-12.02477</t>
+          <t>-11.9534</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>-77.05112</t>
+          <t>-77.0863</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>841</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8437,32 +8437,32 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>649744</t>
+          <t>332783</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - SMP PERU</t>
+          <t>0347 LUIS ENRIQUE XII</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>-12.03164</t>
+          <t>-11.97135</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>-77.06005</t>
+          <t>-77.10592</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>656</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8499,37 +8499,37 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>694656</t>
+          <t>335545</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>JESUS DIVINO MAESTRO</t>
+          <t>SAN PIO X</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>-11.98835</t>
+          <t>-12.0257</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>-77.10532</t>
+          <t>-77.0596</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>419</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8561,32 +8561,32 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>694675</t>
+          <t>333221</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>JUAN PABLO PEREGRINO DE LA PAZ</t>
+          <t>2094 INCA PACHACUTEC</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>-11.97797</t>
+          <t>-12.02112</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>-77.08802</t>
+          <t>-77.0788</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>629</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>694784</t>
+          <t>333264</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>SANTISIMA VIRGEN DEL CAMINO</t>
+          <t>3023 PEDRO E. PAULET MOSTAJO</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>-12.0281</t>
+          <t>-12.0277</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>-77.0654</t>
+          <t>-77.0576</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>826</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8685,32 +8685,32 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>694901</t>
+          <t>336516</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2040 JULIO VIZCARRA AYALA</t>
+          <t>MONITOR HUASCAR</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>-11.9683</t>
+          <t>-11.97989</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>-77.10145</t>
+          <t>-77.09656</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>696</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8747,32 +8747,32 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>695118</t>
+          <t>333320</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO SAVIO DE SAN MARTIN</t>
+          <t>3032 VILLA ANGELICA</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>-12.01649</t>
+          <t>-12.0335471</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>-77.0832</t>
+          <t>-77.0708275</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>807</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8809,37 +8809,37 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>695340</t>
+          <t>596024</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2020 SEÑOR DE LOS MILAGROS</t>
+          <t>HONORABLE ABRAHAM LINCOLN</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>-11.993652</t>
+          <t>-11.98266</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>-77.113069</t>
+          <t>-77.10746</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8871,32 +8871,32 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>695646</t>
+          <t>333122</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN DE ANTARES</t>
+          <t>2031 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>-12.009792</t>
+          <t>-11.98794</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>-77.08447</t>
+          <t>-77.09218</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>900</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8933,32 +8933,32 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>333565</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>CADILLO</t>
+          <t>EL PACIFICO</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>-11.95924</t>
+          <t>-12.0021</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>-77.09929</t>
+          <t>-77.0855</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>701</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8995,32 +8995,32 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>696033</t>
+          <t>332924</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>CHRISTIAN BARNARD COLLEGE</t>
+          <t>2001 SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>-11.965887</t>
+          <t>-11.94492</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>-77.089615</t>
+          <t>-77.08871</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>849</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9057,37 +9057,37 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>696085</t>
+          <t>333551</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>MARIA DE LA ESPERANZA</t>
+          <t>0051 CLORINDA MATTO DE TURNER</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>-12.00763</t>
+          <t>-12.02618</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>-77.08324</t>
+          <t>-77.05959</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>691</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -9119,42 +9119,42 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>696170</t>
+          <t>336917</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>AMISTAD</t>
+          <t>LICEO SAN AGUSTIN</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>-11.9868</t>
+          <t>-11.983133</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>-77.1034</t>
+          <t>-77.094933</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9181,37 +9181,37 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>696448</t>
+          <t>857016</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>PALMER SCHOOL</t>
+          <t>CIENCIAS NEWTON</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>-11.95769</t>
+          <t>-11.985448</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>-77.09423</t>
+          <t>-77.086976</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>95</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9243,37 +9243,37 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>696504</t>
+          <t>333075</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>SEMILLITAS DE IZAGUIRRE DE ARIEL</t>
+          <t>2026 SAN DIEGO</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>-12.01891</t>
+          <t>-11.94765</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>-77.05549</t>
+          <t>-77.093</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -9305,32 +9305,32 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>697565</t>
+          <t>333339</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>CRISTO MISERICORDIOSO</t>
+          <t>3033 ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>-11.97243</t>
+          <t>-12.03575</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>-77.09636</t>
+          <t>-77.08568</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>904</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -9367,32 +9367,32 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>697674</t>
+          <t>333103</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO EL PREDICADOR</t>
+          <t>2029 SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>-11.975037</t>
+          <t>-12.027</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>-77.093511</t>
+          <t>-77.0667</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>799</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -9429,32 +9429,32 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>697805</t>
+          <t>332943</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO</t>
+          <t>2003 LIBERTADOR JOSE DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>-11.9979</t>
+          <t>-12.0063</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>-77.0912</t>
+          <t>-77.091</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -9491,37 +9491,37 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>697872</t>
+          <t>333400</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>3054 VIRGEN DE LAS MERCEDES</t>
+          <t>3041 ANDRES BELLO</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>-11.99143</t>
+          <t>-12.02695</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>-77.1085</t>
+          <t>-77.07982</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>981</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9553,37 +9553,37 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>698678</t>
+          <t>333462</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>SEÑOR DE LA MISERICORDIA</t>
+          <t>3081 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>-12.02663</t>
+          <t>-12.0168</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>-77.0559</t>
+          <t>-77.07513</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9615,42 +9615,42 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>698942</t>
+          <t>332938</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>LOS INGENIEROS DE LOS OLIVOS</t>
+          <t>2002 VIRGEN MARIA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>-11.98885</t>
+          <t>-11.966955</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>-77.08194</t>
+          <t>-77.087685</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9677,32 +9677,32 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>723319</t>
+          <t>332962</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>BH SCHOOL S.M.P.</t>
+          <t>2074 VIRGEN PEREGRINA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>-11.97765</t>
+          <t>-11.97756</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>-77.09389</t>
+          <t>-77.08883</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9712,7 +9712,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9739,32 +9739,32 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>727666</t>
+          <t>335908</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>GENES DE SAN MARTIN DE PORRES</t>
+          <t>HONORES VON BRAUN</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>-11.98937</t>
+          <t>-11.953417</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>-77.08944</t>
+          <t>-77.092469</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>226</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9801,37 +9801,37 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>743421</t>
+          <t>333259</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>MIS TALENTOS DE SAN MARTIN</t>
+          <t>3022 JOSE SABOGAL</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>-12.0324</t>
+          <t>-12.03185</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>-77.0754</t>
+          <t>-77.04596</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -9863,32 +9863,32 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>747848</t>
+          <t>781470</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>FREDERICK TAYLOR</t>
+          <t>INNOVA SCHOOLS - CANTA CALLAO</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>-12.03561</t>
+          <t>-11.96122</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>-77.08732</t>
+          <t>-77.08584</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9925,32 +9925,32 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>752024</t>
+          <t>333594</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>SANTA ANA DE INGENIERIA 01</t>
+          <t>LOS JAZMINES DEL NARANJAL</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>-12.02537</t>
+          <t>-11.9809</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>-77.05005</t>
+          <t>-77.0875</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9987,32 +9987,32 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>754495</t>
+          <t>697674</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>MI PEQUEÑO MUNDO Y LAS ESTRELLITAS</t>
+          <t>SANTO DOMINGO EL PREDICADOR</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>-11.99326</t>
+          <t>-11.975037</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>-77.09962</t>
+          <t>-77.093511</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -10049,32 +10049,32 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>781470</t>
+          <t>333080</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - CANTA CALLAO</t>
+          <t>2027 JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>-11.96122</t>
+          <t>-12.0158</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>-77.08584</t>
+          <t>-77.05705</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -10111,32 +10111,32 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>783695</t>
+          <t>333443</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS DE NARANJAL</t>
+          <t>3045 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>-11.97055</t>
+          <t>-12.026</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>-77.08832</t>
+          <t>-77.0664</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>67</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -10173,37 +10173,37 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>801699</t>
+          <t>336111</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>SANTA ANA DE INGENIERIA 02</t>
+          <t>2009 FE Y ALEGRIA 2</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>-12.02436</t>
+          <t>-12.023</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>-77.0505</t>
+          <t>-77.0755</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>67</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -10235,32 +10235,32 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>802340</t>
+          <t>332844</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE CAYRAN</t>
+          <t>2088 REPUBLICA FEDERAL DE ALEMANIA</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>-11.992562</t>
+          <t>-11.95678</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>-77.084822</t>
+          <t>-77.10062</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -10297,37 +10297,37 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>806084</t>
+          <t>336432</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>SANTA ANA DE LOS JARDINES III</t>
+          <t>VIRGEN DE CZESTOCHOWA</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>-12.01456</t>
+          <t>-12.0312</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>-77.05609</t>
+          <t>-77.0764</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>89</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -10359,32 +10359,32 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>807026</t>
+          <t>333570</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>HENRI WALLON</t>
+          <t>ISABEL CHIMPU OCLLO</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>-12.02962</t>
+          <t>-12.03502</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>-77.09067</t>
+          <t>-77.09341</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>710</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -10421,37 +10421,37 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>807111</t>
+          <t>335687</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>SANTA ANA DE LOS JARDINES II</t>
+          <t>SOCIEDAD EDUCATIVA INGENIERIA SAN SILVESTRE S.A.C.</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>-12.01438</t>
+          <t>-12.02406</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>-77.05571</t>
+          <t>-77.07499</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>151</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10483,37 +10483,37 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>834765</t>
+          <t>335965</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>MI BUEN JESUS</t>
+          <t>PITAGORAS KID'S</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>-12.03549</t>
+          <t>-12.03262</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>-77.09314</t>
+          <t>-77.07546</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>137</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10545,42 +10545,42 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>838947</t>
+          <t>334560</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>CIENCIAS NEWTON</t>
+          <t>CAP. FAP JOSE QUIÑONES</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>-11.985448</t>
+          <t>-12.00107</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>-77.086976</t>
+          <t>-77.08614</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>211</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10607,37 +10607,37 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>839008</t>
+          <t>335201</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>0003 NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>HARVARD SCHOOL S.M.P.</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>-11.9638</t>
+          <t>-12.023256</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>-77.088</t>
+          <t>-77.080931</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -10669,37 +10669,37 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>849125</t>
+          <t>640164</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO SALESIANO</t>
+          <t>SANTA ANA DE INGENIERIA</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>-11.988224</t>
+          <t>-12.02477</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>-77.099364</t>
+          <t>-77.05112</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>169</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -10731,37 +10731,37 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>857016</t>
+          <t>333377</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>CIENCIAS NEWTON</t>
+          <t>3037 GRAN AMAUTA</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>-11.985448</t>
+          <t>-12.0305</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>-77.086976</t>
+          <t>-77.0856</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-SAN_MARTIN_DE_PORRES.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-SAN_MARTIN_DE_PORRES.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>336248</t>
+          <t>857016</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MARTINCITO</t>
+          <t>CIENCIAS NEWTON</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.01639</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.05261</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.985448</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-77.086976</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>572527</t>
+          <t>849125</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ANGELITOS DE JESUS EN TRAVESURAS</t>
+          <t>SAN FRANCISCO SALESIANO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.00844</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.08286</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.988224</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-77.099364</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>696085</t>
+          <t>839008</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MARIA DE LA ESPERANZA</t>
+          <t>0003 NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.00763</t>
+          <t>453</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.08324</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.9638</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-77.088</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,42 +687,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>743421</t>
+          <t>838947</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MIS TALENTOS DE SAN MARTIN</t>
+          <t>CIENCIAS NEWTON</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.0324</t>
+          <t>763</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.0754</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.985448</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-77.086976</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>332716</t>
+          <t>834765</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>MI BUEN JESUS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.99628</t>
+          <t>206</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.09407</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>-12.03549</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.09314</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>694656</t>
+          <t>807111</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JESUS DIVINO MAESTRO</t>
+          <t>SANTA ANA DE LOS JARDINES II</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-11.98835</t>
+          <t>351</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.10532</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>-12.01438</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.05571</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>333424</t>
+          <t>807026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3043 RAMON CASTILLA</t>
+          <t>HENRI WALLON</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.020348</t>
+          <t>271</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.083476</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>-12.02962</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>-77.09067</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>102169</t>
+          <t>806084</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CARDANO VIETE INGENIEROS</t>
+          <t>SANTA ANA DE LOS JARDINES III</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.99788</t>
+          <t>263</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.08956</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>-12.01456</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.05609</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>332684</t>
+          <t>802340</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0011 SAGRADO CORAZON DE JESUS</t>
+          <t>SAN FRANCISCO DE CAYRAN</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.02932</t>
+          <t>232</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.06947</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>-11.992562</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.084822</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,37 +1059,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>332759</t>
+          <t>801699</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0313</t>
+          <t>SANTA ANA DE INGENIERIA 02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.0364</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.0878</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>-12.02436</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.0505</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>332764</t>
+          <t>783695</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>338 MANITOS CREATIVAS</t>
+          <t>SACO OLIVEROS DE NARANJAL</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.02541</t>
+          <t>491</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.08014</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>-11.97055</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.08832</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>332839</t>
+          <t>781470</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0361</t>
+          <t>INNOVA SCHOOLS - CANTA CALLAO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.02818</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.09079</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>-11.96122</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.08584</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>754495</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>LUIS ENRIQUE XIX</t>
+          <t>MI PEQUEÑO MUNDO Y LAS ESTRELLITAS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.01774</t>
+          <t>244</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.07859</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>-11.99326</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.09962</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>334635</t>
+          <t>752024</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SAN ANTONIO DE PADUA</t>
+          <t>SANTA ANA DE INGENIERIA 01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.01125</t>
+          <t>261</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.05723</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>-12.02537</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.05005</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>617984</t>
+          <t>747848</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HONORES</t>
+          <t>FREDERICK TAYLOR</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-11.959931</t>
+          <t>373</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.097146</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>-12.03561</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.08732</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,37 +1431,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>696170</t>
+          <t>743421</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AMISTAD</t>
+          <t>MIS TALENTOS DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-11.9868</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.1034</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>-12.0324</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.0754</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>754495</t>
+          <t>727666</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MI PEQUEÑO MUNDO Y LAS ESTRELLITAS</t>
+          <t>GENES DE SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.99326</t>
+          <t>826</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.09962</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>-11.98937</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.08944</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>807026</t>
+          <t>723319</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>HENRI WALLON</t>
+          <t>BH SCHOOL S.M.P.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.02962</t>
+          <t>260</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.09067</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>-11.97765</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.09389</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,37 +1617,37 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>807111</t>
+          <t>698942</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SANTA ANA DE LOS JARDINES II</t>
+          <t>LOS INGENIEROS DE LOS OLIVOS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.01438</t>
+          <t>184</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.05571</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>-11.98885</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.08194</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1679,37 +1679,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>849125</t>
+          <t>698678</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO SALESIANO</t>
+          <t>SEÑOR DE LA MISERICORDIA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-11.988224</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.099364</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>-12.02663</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.0559</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1741,37 +1741,37 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>332976</t>
+          <t>697872</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2010 ALBERT EINSTEIN</t>
+          <t>3054 VIRGEN DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.017275</t>
+          <t>264</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.087375</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>-11.99143</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.1085</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>695340</t>
+          <t>697805</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2020 SEÑOR DE LOS MILAGROS</t>
+          <t>CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-11.993652</t>
+          <t>424</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.113069</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>-11.9979</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.0912</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>696033</t>
+          <t>697674</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CHRISTIAN BARNARD COLLEGE</t>
+          <t>SANTO DOMINGO EL PREDICADOR</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-11.965887</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.089615</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>-11.975037</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.093511</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>802340</t>
+          <t>697565</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE CAYRAN</t>
+          <t>CRISTO MISERICORDIOSO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-11.992562</t>
+          <t>399</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.084822</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>-11.97243</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.09636</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,37 +1989,37 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>332740</t>
+          <t>696504</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0081 LA SONRISA DE DIOS</t>
+          <t>SEMILLITAS DE IZAGUIRRE DE ARIEL</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.019886</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.086935</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>-12.01891</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.05549</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>335220</t>
+          <t>696448</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HENRI WALLON</t>
+          <t>PALMER SCHOOL</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.02992</t>
+          <t>519</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.0907</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>-11.95769</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.09423</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,37 +2113,37 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>526229</t>
+          <t>696170</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SAN MARTIN DE LOS ALGARROBOS</t>
+          <t>AMISTAD</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-11.97025</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.10866</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>-11.9868</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.1034</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2175,37 +2175,37 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>752024</t>
+          <t>696085</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SANTA ANA DE INGENIERIA 01</t>
+          <t>MARIA DE LA ESPERANZA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.02537</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.05005</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>-12.00763</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.08324</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>333004</t>
+          <t>696033</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>CHRISTIAN BARNARD COLLEGE</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.03451</t>
+          <t>334</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.05606</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>-11.965887</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.089615</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>333018</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2014 LOS CHASQUIS</t>
+          <t>CADILLO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-11.993831</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.097146</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>-11.95924</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.09929</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>333481</t>
+          <t>695646</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>SAN AGUSTIN DE ANTARES</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-11.96584</t>
+          <t>251</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.08469</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>-12.009792</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.08447</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,37 +2423,37 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>334225</t>
+          <t>695340</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MAGDA PORTAL</t>
+          <t>2020 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.03106</t>
+          <t>292</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-77.09005</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>-11.993652</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.113069</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>334428</t>
+          <t>695118</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RODMAR SCHOOL</t>
+          <t>SANTO DOMINGO SAVIO DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.026833</t>
+          <t>376</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.051583</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>-12.01649</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.0832</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>335951</t>
+          <t>694901</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PERUANO CANADIENSE SAN DIEGO COLLEGE</t>
+          <t>2040 JULIO VIZCARRA AYALA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-11.9495</t>
+          <t>611</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-77.0911</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>-11.9683</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.10145</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>806084</t>
+          <t>694784</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SANTA ANA DE LOS JARDINES III</t>
+          <t>SANTISIMA VIRGEN DEL CAMINO</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.01456</t>
+          <t>209</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-77.05609</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>-12.0281</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.0654</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>332655</t>
+          <t>694675</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0005</t>
+          <t>JUAN PABLO PEREGRINO DE LA PAZ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-11.94575</t>
+          <t>545</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-77.08906</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>-11.97797</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.08802</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,37 +2733,37 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>334409</t>
+          <t>694656</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>NIELS BOHR</t>
+          <t>JESUS DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-11.98623</t>
+          <t>168</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-77.09812</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>-11.98835</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.10532</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>334999</t>
+          <t>649744</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>VIRGEN DE GUADALUPE</t>
+          <t>INNOVA SCHOOLS - SMP PERU</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-11.94735</t>
+          <t>872</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-77.08795</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>-12.03164</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.06005</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2857,37 +2857,37 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>336903</t>
+          <t>640164</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>LORD BRAIN</t>
+          <t>SANTA ANA DE INGENIERIA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-11.97131</t>
+          <t>169</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-77.09665</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>-12.02477</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.05112</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>336955</t>
+          <t>619643</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FRANCISCA DIEZ CANSECO DE CASTILLA</t>
+          <t>JUAN PABLO PEREGRINO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-11.97188</t>
+          <t>362</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-77.1004</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>-11.98381</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.08954</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>525121</t>
+          <t>617984</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>INGENIERIA DE CONDEVILLA</t>
+          <t>HONORES</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.02237</t>
+          <t>257</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-77.09025</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>-11.959931</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.097146</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>537218</t>
+          <t>604081</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>DOMINGO SAVIO DE SAN MARTIN I</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.016194</t>
+          <t>574</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-77.083097</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>-12.03431</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.08767</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3105,37 +3105,37 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>570726</t>
+          <t>596024</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SANTA TERESA DE JESUS - SOPHIANUM</t>
+          <t>HONORABLE ABRAHAM LINCOLN</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-11.996865</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-77.098168</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>-11.98266</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.10746</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>332735</t>
+          <t>594591</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0065</t>
+          <t>HONORES OQUENDO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.02645</t>
+          <t>664</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-77.06532</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>-11.97957</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.11181</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,37 +3229,37 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>332882</t>
+          <t>572527</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CONDEVILLA SEÑOR I</t>
+          <t>ANGELITOS DE JESUS EN TRAVESURAS</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.0214</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-77.0814</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>-12.00844</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.08286</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>333297</t>
+          <t>570726</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>3028 YACHAYHUASI</t>
+          <t>SANTA TERESA DE JESUS - SOPHIANUM</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-11.99239</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-77.08455</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>-11.996865</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.098168</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>333589</t>
+          <t>537218</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>JOSE HECTOR RODRIGUEZ TRIGOSO</t>
+          <t>DOMINGO SAVIO DE SAN MARTIN I</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-12.01502</t>
+          <t>278</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-77.07384</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>-12.016194</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.083097</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>334065</t>
+          <t>526328</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>JUAN XXIII</t>
+          <t>3035 BELLA LETICIA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.01206</t>
+          <t>490</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-77.05993</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>-12.0341</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.062</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>336644</t>
+          <t>526229</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>PABLO PICASSO</t>
+          <t>SAN MARTIN DE LOS ALGARROBOS</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.02293</t>
+          <t>256</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-77.06286</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>-11.97025</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.10866</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>512208</t>
+          <t>525121</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SANTA MARIA PURISIMA</t>
+          <t>INGENIERIA DE CONDEVILLA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-11.96392</t>
+          <t>362</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-77.10533</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>-12.02237</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.09025</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>783695</t>
+          <t>512208</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS DE NARANJAL</t>
+          <t>SANTA MARIA PURISIMA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-11.97055</t>
+          <t>299</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-77.08832</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>-11.96392</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.10533</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,37 +3663,37 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>332721</t>
+          <t>506735</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0057</t>
+          <t>PRIMERA NATURALEZA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-12.03451</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-77.05563</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>-12.00397</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.08392</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>333235</t>
+          <t>504760</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2098 CABO JESUS VERA FERNANDEZ</t>
+          <t>TECHNOLOGY SCHOOLS CAYETANO</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-12.01285</t>
+          <t>629</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-77.06808</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>-12.02445</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.05789</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>333363</t>
+          <t>337356</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>3036 JOSE ANDRES RAZURI</t>
+          <t>TECHNOLOGY SCHOOLS DE SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-12.0367</t>
+          <t>394</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-77.0905</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>-11.99315</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.09957</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>334895</t>
+          <t>337281</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
+          <t>SANTA ANA DE LOS JARDINES</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-12.02417</t>
+          <t>744</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-77.06377</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>-12.01399</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.05519</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>504760</t>
+          <t>336955</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TECHNOLOGY SCHOOLS CAYETANO</t>
+          <t>FRANCISCA DIEZ CANSECO DE CASTILLA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-12.02445</t>
+          <t>334</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-77.05789</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>-11.97188</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.1004</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>694784</t>
+          <t>336917</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SANTISIMA VIRGEN DEL CAMINO</t>
+          <t>LICEO SAN AGUSTIN</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-12.0281</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-77.0654</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>-11.983133</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.094933</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>336903</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CADILLO</t>
+          <t>LORD BRAIN</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-11.95924</t>
+          <t>347</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-77.09929</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>-11.97131</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.09665</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>332863</t>
+          <t>336738</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>0387 NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>VILLA AMERICA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-12.0062</t>
+          <t>299</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-77.08523</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>-11.9954</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.0853</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>335102</t>
+          <t>336677</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ARQUITECTOS SCHOOL</t>
+          <t>LOS DOMINICOS DE PALAO</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-12.03543</t>
+          <t>325</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-77.08092</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>-12.01576</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.05589</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>336677</t>
+          <t>336644</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>LOS DOMINICOS DE PALAO</t>
+          <t>PABLO PICASSO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-12.01576</t>
+          <t>247</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-77.05589</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>-12.02293</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.06286</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,37 +4283,37 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>336738</t>
+          <t>336564</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>VILLA AMERICA</t>
+          <t>MAGDA PORTAL</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-11.9954</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-77.0853</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>-12.03112</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.08909</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>604081</t>
+          <t>336516</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>MONITOR HUASCAR</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-12.03431</t>
+          <t>696</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-77.08767</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>-11.97989</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.09656</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,37 +4407,37 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>695646</t>
+          <t>336432</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN DE ANTARES</t>
+          <t>VIRGEN DE CZESTOCHOWA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-12.009792</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-77.08447</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>-12.0312</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.0764</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>697565</t>
+          <t>336371</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CRISTO MISERICORDIOSO</t>
+          <t>SAN JOSE DE CLUNY</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-11.97243</t>
+          <t>355</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-77.09636</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>-12.00111</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.09302</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,37 +4531,37 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>697872</t>
+          <t>336328</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>3054 VIRGEN DE LAS MERCEDES</t>
+          <t>SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-11.99143</t>
+          <t>449</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-77.1085</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>-11.99206</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.10166</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>333438</t>
+          <t>336253</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>3044 RICARDO PALMA</t>
+          <t>SAN MIGUEL ARCANGEL</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-12.02672</t>
+          <t>359</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-77.07093</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>-11.960267</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.086567</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,37 +4655,37 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>333688</t>
+          <t>336248</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CORONEL JUAN VALER SANDOVAL</t>
+          <t>MARTINCITO</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-12.01772</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-77.08153</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>-12.01639</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.05261</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>334452</t>
+          <t>336234</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA NATIVIDAD</t>
+          <t>SANTISIMA VIRGEN DE LA PUERTA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-12.03373</t>
+          <t>542</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-77.05095</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>-12.00728</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.09126</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4779,37 +4779,37 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>336564</t>
+          <t>336229</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MAGDA PORTAL</t>
+          <t>ABRAHAM LINCOLN COLLEGE</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-12.03112</t>
+          <t>456</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-77.08909</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-12.0149</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-77.0761</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>333117</t>
+          <t>336111</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2030 VIRGEN DEL CARMEN</t>
+          <t>2009 FE Y ALEGRIA 2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-12.00012</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-77.08946</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>-12.023</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.0755</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4903,37 +4903,37 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>333650</t>
+          <t>335965</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2075 NUEVO AMANECER</t>
+          <t>PITAGORAS KID'S</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-12.018525</t>
+          <t>137</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-77.067375</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>-12.03262</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.07546</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4965,37 +4965,37 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>334471</t>
+          <t>335951</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL CARMEN DE PALAO</t>
+          <t>PERUANO CANADIENSE SAN DIEGO COLLEGE</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-12.01883</t>
+          <t>320</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-77.05392</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>-11.9495</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.0911</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>695118</t>
+          <t>335932</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO SAVIO DE SAN MARTIN</t>
+          <t>SAN FRANCISCO DE CAYRAN</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-12.01649</t>
+          <t>439</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-77.0832</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>-11.99265</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.08474</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5089,37 +5089,37 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>698942</t>
+          <t>335908</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>LOS INGENIEROS DE LOS OLIVOS</t>
+          <t>HONORES VON BRAUN</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-11.98885</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-77.08194</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>-11.953417</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.092469</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>839008</t>
+          <t>335852</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>0003 NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>SANTO TOMAS DE AQUINO DE LOS JARDIN / SANTO TOMAS DE AQUINO DE LOS JARDINES</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-11.9638</t>
+          <t>571</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-77.088</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>-12.01357</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.05473</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5213,37 +5213,37 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>333202</t>
+          <t>335687</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>LOS ALISOS</t>
+          <t>SOCIEDAD EDUCATIVA INGENIERIA SAN SILVESTRE S.A.C.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-11.9848</t>
+          <t>151</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-77.087875</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>-12.02406</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.07499</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>333419</t>
+          <t>335545</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>3042 JESUS EL SALVADOR</t>
+          <t>SAN PIO X</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-12.03108</t>
+          <t>419</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-77.06975</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>-12.0257</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.0596</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>335178</t>
+          <t>335338</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>EL NUEVO MARIANNE FROSTIG</t>
+          <t>JUAN PABLO AYLLON HERRERA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-12.01393</t>
+          <t>264</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-77.07531</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>-12.007768</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.088833</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>335338</t>
+          <t>335220</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>JUAN PABLO AYLLON HERRERA</t>
+          <t>HENRI WALLON</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-12.007768</t>
+          <t>245</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-77.088833</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>-12.02992</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.0907</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5461,37 +5461,37 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>336253</t>
+          <t>335201</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SAN MIGUEL ARCANGEL</t>
+          <t>HARVARD SCHOOL S.M.P.</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-11.960267</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-77.086567</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>-12.023256</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.080931</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>619643</t>
+          <t>335178</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>JUAN PABLO PEREGRINO</t>
+          <t>EL NUEVO MARIANNE FROSTIG</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-11.98381</t>
+          <t>388</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-77.08954</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>-12.01393</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.07531</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>723319</t>
+          <t>335102</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>BH SCHOOL S.M.P.</t>
+          <t>ARQUITECTOS SCHOOL</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-11.97765</t>
+          <t>215</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-77.09389</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>-12.03543</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.08092</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>332957</t>
+          <t>334999</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2008 EL ROSARIO</t>
+          <t>VIRGEN DE GUADALUPE</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-12.02069</t>
+          <t>258</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-77.07389</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>-11.94735</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.08795</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>333155</t>
+          <t>334895</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2034 VIRGEN DE FATIMA</t>
+          <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-12.0115</t>
+          <t>270</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-77.05794</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>-12.02417</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.06377</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5771,37 +5771,37 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>335932</t>
+          <t>334763</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE CAYRAN</t>
+          <t>SANTA ANA DE INGENIERIA</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-11.99265</t>
+          <t>683</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-77.08474</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>-12.02474</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.05052</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>336328</t>
+          <t>334635</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DE LOYOLA</t>
+          <t>SAN ANTONIO DE PADUA</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-11.99206</t>
+          <t>205</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-77.10166</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>-12.01125</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.05723</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>697805</t>
+          <t>334560</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO</t>
+          <t>CAP. FAP JOSE QUIÑONES</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-11.9979</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-77.0912</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>-12.00107</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.08614</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>80860</t>
+          <t>334555</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>VANGUARD SCHOOLS</t>
+          <t>REINO DE LOS CIELOS</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-12.01391</t>
+          <t>268</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-77.08558</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>-12.024078</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.054689</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6019,37 +6019,37 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>333179</t>
+          <t>334471</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2072 MARIO VARGAS LLOSA</t>
+          <t>NUESTRA SEÑORA DEL CARMEN DE PALAO</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-11.9982</t>
+          <t>373</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-77.0954</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>-12.01883</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.05392</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6081,32 +6081,32 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>333382</t>
+          <t>334466</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>3038 PATRICIA CARMEN GUZMAN</t>
+          <t>NUESTRA SEÑORA DE LA PAZ</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-12.0272</t>
+          <t>407</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-77.08883</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>-12.0112</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.08578</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6143,32 +6143,32 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>334206</t>
+          <t>334452</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>LUIS E. GALVAN</t>
+          <t>NUESTRA SEÑORA DE LA NATIVIDAD</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-12.03162</t>
+          <t>205</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-77.06179</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>-12.03373</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.05095</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6205,32 +6205,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>336371</t>
+          <t>334428</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SAN JOSE DE CLUNY</t>
+          <t>RODMAR SCHOOL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-12.00111</t>
+          <t>236</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-77.09302</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>-12.026833</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.051583</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>337281</t>
+          <t>334409</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>SANTA ANA DE LOS JARDINES</t>
+          <t>NIELS BOHR</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-12.01399</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-77.05519</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>-11.98623</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.09812</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6329,37 +6329,37 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>312313</t>
+          <t>334225</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ANA MARIA RIVIER</t>
+          <t>MAGDA PORTAL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-11.97685</t>
+          <t>174</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-77.08641</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>-12.03106</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.09005</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>332815</t>
+          <t>334206</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>0358 NIÑO JESUS DE PRAGA</t>
+          <t>LUIS E. GALVAN</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-12.00635</t>
+          <t>205</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-77.09065</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>-12.03162</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.06179</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>332896</t>
+          <t>334065</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CONDEVILLA SEÑOR II</t>
+          <t>JUAN XXIII</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-12.0243</t>
+          <t>229</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-77.0735</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>-12.01206</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.05993</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6515,37 +6515,37 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>333240</t>
+          <t>333749</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2101 MARIA AUXILIADORA</t>
+          <t>CESAR VALLEJO MENDOZA</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-12.0158</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-77.0777</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>-12.03276</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.06794</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6577,32 +6577,32 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>337356</t>
+          <t>333688</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>TECHNOLOGY SCHOOLS DE SAN MARTIN DE PORRES</t>
+          <t>CORONEL JUAN VALER SANDOVAL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-11.99315</t>
+          <t>418</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>-77.09957</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>-12.01772</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.08153</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>594591</t>
+          <t>333674</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>HONORES OQUENDO</t>
+          <t>3082 PARAISO FLORIDO</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-11.97957</t>
+          <t>614</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>-77.11181</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>-11.9876</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.1014</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6701,32 +6701,32 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>332995</t>
+          <t>333650</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2075 NUEVO AMANECER</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-12.0177</t>
+          <t>340</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-77.062</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>-12.018525</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-77.067375</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6763,32 +6763,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>333141</t>
+          <t>333594</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2033 CARLOS HIRAOKA TORRES</t>
+          <t>LOS JAZMINES DEL NARANJAL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-11.98562</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-77.09974</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>-11.9809</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-77.0875</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6825,32 +6825,32 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>334555</t>
+          <t>333589</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>REINO DE LOS CIELOS</t>
+          <t>JOSE HECTOR RODRIGUEZ TRIGOSO</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-12.024078</t>
+          <t>301</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>-77.054689</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>-12.01502</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-77.07384</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6887,37 +6887,37 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>334763</t>
+          <t>333570</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>SANTA ANA DE INGENIERIA</t>
+          <t>ISABEL CHIMPU OCLLO</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-12.02474</t>
+          <t>710</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>-77.05052</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>-12.03502</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-77.09341</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6949,32 +6949,32 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>336229</t>
+          <t>333565</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>ABRAHAM LINCOLN COLLEGE</t>
+          <t>EL PACIFICO</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-12.0149</t>
+          <t>701</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>-77.0761</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>-12.0021</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-77.0855</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -7011,32 +7011,32 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>747848</t>
+          <t>333551</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FREDERICK TAYLOR</t>
+          <t>0051 CLORINDA MATTO DE TURNER</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-12.03561</t>
+          <t>691</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>-77.08732</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>-12.02618</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-77.05959</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7073,32 +7073,32 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>526328</t>
+          <t>333532</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>3035 BELLA LETICIA</t>
+          <t>2073 JOSE OLAYA BALANDRA</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-12.0341</t>
+          <t>841</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>-77.062</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>-11.9534</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-77.0863</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -7135,32 +7135,32 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>694675</t>
+          <t>333481</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>JUAN PABLO PEREGRINO DE LA PAZ</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-11.97797</t>
+          <t>325</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>-77.08802</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>-11.96584</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-77.08469</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7197,42 +7197,42 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>838947</t>
+          <t>333462</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CIENCIAS NEWTON</t>
+          <t>3081 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-11.985448</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>-77.086976</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>-12.0168</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-77.07513</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7259,32 +7259,32 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>335852</t>
+          <t>333443</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>SANTO TOMAS DE AQUINO DE LOS JARDIN / SANTO TOMAS DE AQUINO DE LOS JARDINES</t>
+          <t>3045 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-12.01357</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>-77.05473</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>-12.026</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-77.0664</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7321,32 +7321,32 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>333198</t>
+          <t>333438</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2082 HEROES DEL PACIFICO</t>
+          <t>3044 RICARDO PALMA</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-12.00299</t>
+          <t>351</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>-77.08484</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>-12.02672</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-77.07093</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7383,32 +7383,32 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>333749</t>
+          <t>333424</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO MENDOZA</t>
+          <t>3043 RAMON CASTILLA</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-12.03276</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>-77.06794</t>
+          <t>103</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>-12.020348</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-77.083476</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7445,32 +7445,32 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>649744</t>
+          <t>333419</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - SMP PERU</t>
+          <t>3042 JESUS EL SALVADOR</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-12.03164</t>
+          <t>475</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>-77.06005</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>-12.03108</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-77.06975</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7507,32 +7507,32 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>694901</t>
+          <t>333400</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2040 JULIO VIZCARRA AYALA</t>
+          <t>3041 ANDRES BELLO</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-11.9683</t>
+          <t>981</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>-77.10145</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>-12.02695</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-77.07982</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -7569,32 +7569,32 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>696448</t>
+          <t>333382</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>PALMER SCHOOL</t>
+          <t>3038 PATRICIA CARMEN GUZMAN</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-11.95769</t>
+          <t>511</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>-77.09423</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>-12.0272</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-77.08883</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7631,37 +7631,37 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>333315</t>
+          <t>333377</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>3031 GRANDES TALENTOS</t>
+          <t>3037 GRAN AMAUTA</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-12.03674</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>-77.04585</t>
+          <t>94</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-12.0305</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-77.0856</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7693,37 +7693,37 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>506735</t>
+          <t>333363</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>PRIMERA NATURALEZA</t>
+          <t>3036 JOSE ANDRES RAZURI</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-12.00397</t>
+          <t>325</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>-77.08392</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-12.0367</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-77.0905</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7755,37 +7755,37 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>696504</t>
+          <t>333339</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SEMILLITAS DE IZAGUIRRE DE ARIEL</t>
+          <t>3033 ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-12.01891</t>
+          <t>904</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>-77.05549</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-12.03575</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-77.08568</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7817,42 +7817,42 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>698678</t>
+          <t>333320</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SEÑOR DE LA MISERICORDIA</t>
+          <t>3032 VILLA ANGELICA</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-12.02663</t>
+          <t>807</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>-77.0559</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-12.0335471</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-77.0708275</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7879,32 +7879,32 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>801699</t>
+          <t>333315</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SANTA ANA DE INGENIERIA 02</t>
+          <t>3031 GRANDES TALENTOS</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-12.02436</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>-77.0505</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-12.03674</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-77.04585</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7941,37 +7941,37 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>313435</t>
+          <t>333297</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>EL NAZARENO</t>
+          <t>3028 YACHAYHUASI</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-11.9633</t>
+          <t>387</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>-77.0922</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>-11.99239</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-77.08455</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8003,32 +8003,32 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>336234</t>
+          <t>333283</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SANTISIMA VIRGEN DE LA PUERTA</t>
+          <t>3027 CORONEL JOSE BALTA</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-12.00728</t>
+          <t>403</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>-77.09126</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>-12.03106</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-77.05296</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8065,32 +8065,32 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>727666</t>
+          <t>333264</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>GENES DE SAN MARTIN DE PORRES</t>
+          <t>3023 PEDRO E. PAULET MOSTAJO</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-11.98937</t>
+          <t>826</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>-77.08944</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>-12.0277</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-77.0576</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8127,32 +8127,32 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>834765</t>
+          <t>333259</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>MI BUEN JESUS</t>
+          <t>3022 JOSE SABOGAL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-12.03549</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>-77.09314</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>-12.03185</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-77.04596</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8189,42 +8189,42 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>333674</t>
+          <t>333240</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>3082 PARAISO FLORIDO</t>
+          <t>2101 MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-11.9876</t>
+          <t>517</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>-77.1014</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>-12.0158</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-77.0777</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8251,32 +8251,32 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>333283</t>
+          <t>333235</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>3027 CORONEL JOSE BALTA</t>
+          <t>2098 CABO JESUS VERA FERNANDEZ</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>-12.03106</t>
+          <t>282</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>-77.05296</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>-12.01285</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-77.06808</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8313,32 +8313,32 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>334466</t>
+          <t>333221</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA PAZ</t>
+          <t>2094 INCA PACHACUTEC</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>-12.0112</t>
+          <t>629</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>-77.08578</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>-12.02112</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-77.0788</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -8375,32 +8375,32 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>333532</t>
+          <t>333202</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2073 JOSE OLAYA BALANDRA</t>
+          <t>LOS ALISOS</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>-11.9534</t>
+          <t>492</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>-77.0863</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>-11.9848</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-77.087875</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -8437,32 +8437,32 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>332783</t>
+          <t>333198</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>0347 LUIS ENRIQUE XII</t>
+          <t>2082 HEROES DEL PACIFICO</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>-11.97135</t>
+          <t>570</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>-77.10592</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>-12.00299</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-77.08484</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -8499,32 +8499,32 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>335545</t>
+          <t>333179</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SAN PIO X</t>
+          <t>2072 MARIO VARGAS LLOSA</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>-12.0257</t>
+          <t>595</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>-77.0596</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>-11.9982</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-77.0954</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -8561,32 +8561,32 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>333221</t>
+          <t>333155</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2094 INCA PACHACUTEC</t>
+          <t>2034 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>-12.02112</t>
+          <t>465</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>-77.0788</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>-12.0115</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-77.05794</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>333264</t>
+          <t>333141</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>3023 PEDRO E. PAULET MOSTAJO</t>
+          <t>2033 CARLOS HIRAOKA TORRES</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>-12.0277</t>
+          <t>542</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>-77.0576</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>-11.98562</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-77.09974</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8685,32 +8685,32 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>336516</t>
+          <t>333122</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>MONITOR HUASCAR</t>
+          <t>2031 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>-11.97989</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>-77.09656</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>-11.98794</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-77.09218</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8747,32 +8747,32 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>333320</t>
+          <t>333117</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>3032 VILLA ANGELICA</t>
+          <t>2030 VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>-12.0335471</t>
+          <t>455</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>-77.0708275</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>-12.00012</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-77.08946</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8809,37 +8809,37 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>596024</t>
+          <t>333103</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>HONORABLE ABRAHAM LINCOLN</t>
+          <t>2029 SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>-11.98266</t>
+          <t>799</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>-77.10746</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-12.027</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-77.0667</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8871,32 +8871,32 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>333122</t>
+          <t>333080</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2031 VIRGEN DE FATIMA</t>
+          <t>2027 JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>-11.98794</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>-77.09218</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>-12.0158</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-77.05705</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8933,32 +8933,32 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>333565</t>
+          <t>333075</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>EL PACIFICO</t>
+          <t>2026 SAN DIEGO</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>-12.0021</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>-77.0855</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>-11.94765</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-77.093</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8995,32 +8995,32 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>332924</t>
+          <t>333018</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2001 SANTA ROSA DE LIMA</t>
+          <t>2014 LOS CHASQUIS</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>-11.94492</t>
+          <t>346</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>-77.08871</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>-11.993831</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-77.097146</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9057,32 +9057,32 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>333551</t>
+          <t>333004</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>0051 CLORINDA MATTO DE TURNER</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>-12.02618</t>
+          <t>327</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>-77.05959</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>-12.03451</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-77.05606</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9119,32 +9119,32 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>336917</t>
+          <t>332995</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>LICEO SAN AGUSTIN</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>-11.983133</t>
+          <t>490</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>-77.094933</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>-12.0177</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-77.062</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9181,37 +9181,37 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>857016</t>
+          <t>332976</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>CIENCIAS NEWTON</t>
+          <t>2010 ALBERT EINSTEIN</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>-11.985448</t>
+          <t>455</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>-77.086976</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>-12.017275</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-77.087375</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9243,32 +9243,32 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>333075</t>
+          <t>332962</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026 SAN DIEGO</t>
+          <t>2074 VIRGEN PEREGRINA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>-11.94765</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>-77.093</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>-11.97756</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-77.08883</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9305,32 +9305,32 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>333339</t>
+          <t>332957</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>3033 ANDRES AVELINO CACERES</t>
+          <t>2008 EL ROSARIO</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>-12.03575</t>
+          <t>484</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>-77.08568</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>-12.02069</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-77.07389</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -9367,32 +9367,32 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>333103</t>
+          <t>332943</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2029 SIMON BOLIVAR</t>
+          <t>2003 LIBERTADOR JOSE DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>-12.027</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>-77.0667</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>-12.0063</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-77.091</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -9429,32 +9429,32 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>332943</t>
+          <t>332938</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2003 LIBERTADOR JOSE DE SAN MARTIN</t>
+          <t>2002 VIRGEN MARIA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>-12.0063</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>-77.091</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>-11.966955</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-77.087685</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9491,32 +9491,32 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>333400</t>
+          <t>332924</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>3041 ANDRES BELLO</t>
+          <t>2001 SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>-12.02695</t>
+          <t>849</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>-77.07982</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>-11.94492</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-77.08871</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9553,32 +9553,32 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>333462</t>
+          <t>332900</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>3081 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
+          <t>LUIS ENRIQUE XIX</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>-12.0168</t>
+          <t>227</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>-77.07513</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>-12.01774</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>-77.07859</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -9615,32 +9615,32 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>332938</t>
+          <t>332896</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2002 VIRGEN MARIA DEL ROSARIO</t>
+          <t>CONDEVILLA SEÑOR II</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>-11.966955</t>
+          <t>317</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>-77.087685</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>-12.0243</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-77.0735</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9677,32 +9677,32 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>332962</t>
+          <t>332882</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2074 VIRGEN PEREGRINA DEL ROSARIO</t>
+          <t>CONDEVILLA SEÑOR I</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>-11.97756</t>
+          <t>308</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>-77.08883</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>-12.0214</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-77.0814</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9712,7 +9712,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9739,32 +9739,32 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>335908</t>
+          <t>332863</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>HONORES VON BRAUN</t>
+          <t>0387 NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>-11.953417</t>
+          <t>392</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>-77.092469</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>-12.0062</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-77.08523</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9801,32 +9801,32 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>333259</t>
+          <t>332844</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>3022 JOSE SABOGAL</t>
+          <t>2088 REPUBLICA FEDERAL DE ALEMANIA</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>-12.03185</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>-77.04596</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>-11.95678</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-77.10062</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -9863,32 +9863,32 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>781470</t>
+          <t>332839</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - CANTA CALLAO</t>
+          <t>0361</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>-11.96122</t>
+          <t>208</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>-77.08584</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>-12.02818</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>-77.09079</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9925,32 +9925,32 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>333594</t>
+          <t>332815</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>LOS JAZMINES DEL NARANJAL</t>
+          <t>0358 NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>-11.9809</t>
+          <t>454</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>-77.0875</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>-12.00635</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-77.09065</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9987,32 +9987,32 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>697674</t>
+          <t>332783</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO EL PREDICADOR</t>
+          <t>0347 LUIS ENRIQUE XII</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>-11.975037</t>
+          <t>656</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>-77.093511</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>-11.97135</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-77.10592</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -10049,32 +10049,32 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>333080</t>
+          <t>332764</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2027 JOSE MARIA ARGUEDAS</t>
+          <t>338 MANITOS CREATIVAS</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>-12.0158</t>
+          <t>230</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>-77.05705</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>-12.02541</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-77.08014</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10111,32 +10111,32 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>333443</t>
+          <t>332759</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>3045 JOSE CARLOS MARIATEGUI</t>
+          <t>0313</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>-12.026</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>-77.0664</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>-12.0364</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>-77.0878</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -10173,32 +10173,32 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>336111</t>
+          <t>332740</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2009 FE Y ALEGRIA 2</t>
+          <t>0081 LA SONRISA DE DIOS</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>-12.023</t>
+          <t>258</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>-77.0755</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>-12.019886</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>-77.086935</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -10235,32 +10235,32 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>332844</t>
+          <t>332735</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2088 REPUBLICA FEDERAL DE ALEMANIA</t>
+          <t>0065</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>-11.95678</t>
+          <t>345</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>-77.10062</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>-12.02645</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-77.06532</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -10297,37 +10297,37 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>336432</t>
+          <t>332721</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>VIRGEN DE CZESTOCHOWA</t>
+          <t>0057</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>-12.0312</t>
+          <t>347</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>-77.0764</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>-12.03451</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-77.05563</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -10359,32 +10359,32 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>333570</t>
+          <t>332716</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>ISABEL CHIMPU OCLLO</t>
+          <t>0020</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>-12.03502</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>-77.09341</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>-11.99628</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>-77.09407</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -10421,37 +10421,37 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>335687</t>
+          <t>332684</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>SOCIEDAD EDUCATIVA INGENIERIA SAN SILVESTRE S.A.C.</t>
+          <t>0011 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>-12.02406</t>
+          <t>247</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>-77.07499</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>-12.02932</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-77.06947</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10483,37 +10483,37 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>335965</t>
+          <t>332655</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>PITAGORAS KID'S</t>
+          <t>0005</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>-12.03262</t>
+          <t>317</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>-77.07546</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>-11.94575</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-77.08906</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10545,37 +10545,37 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>334560</t>
+          <t>313435</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>CAP. FAP JOSE QUIÑONES</t>
+          <t>EL NAZARENO</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>-12.00107</t>
+          <t>703</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>-77.08614</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>-11.9633</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-77.0922</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10607,37 +10607,37 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>335201</t>
+          <t>312313</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>HARVARD SCHOOL S.M.P.</t>
+          <t>ANA MARIA RIVIER</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>-12.023256</t>
+          <t>203</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>-77.080931</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-11.97685</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-77.08641</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -10669,37 +10669,37 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>640164</t>
+          <t>102169</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>SANTA ANA DE INGENIERIA</t>
+          <t>CARDANO VIETE INGENIEROS</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>-12.02477</t>
+          <t>545</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>-77.05112</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>-11.99788</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-77.08956</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -10731,32 +10731,32 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>333377</t>
+          <t>080860</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>3037 GRAN AMAUTA</t>
+          <t>VANGUARD SCHOOLS</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>-12.0305</t>
+          <t>403</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>-77.0856</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>-12.01391</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>-77.08558</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-SAN_MARTIN_DE_PORRES.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-SAN_MARTIN_DE_PORRES.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
